--- a/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>LX</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>421900</v>
+        <v>487800</v>
       </c>
       <c r="E8" s="3">
-        <v>411900</v>
+        <v>424800</v>
       </c>
       <c r="F8" s="3">
-        <v>421200</v>
+        <v>414700</v>
       </c>
       <c r="G8" s="3">
-        <v>371500</v>
+        <v>424100</v>
       </c>
       <c r="H8" s="3">
-        <v>333200</v>
+        <v>374000</v>
       </c>
       <c r="I8" s="3">
-        <v>236400</v>
+        <v>335400</v>
       </c>
       <c r="J8" s="3">
+        <v>238100</v>
+      </c>
+      <c r="K8" s="3">
         <v>303700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>422000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>464700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>422800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>422200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>464800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>435900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>394400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>484700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>490900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>388900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>269900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>370200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>258900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>285400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>231500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>236500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>215600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>195500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>177200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>202100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>284500</v>
+        <v>299300</v>
       </c>
       <c r="E9" s="3">
-        <v>287200</v>
+        <v>286400</v>
       </c>
       <c r="F9" s="3">
-        <v>277100</v>
+        <v>289100</v>
       </c>
       <c r="G9" s="3">
-        <v>247600</v>
+        <v>279000</v>
       </c>
       <c r="H9" s="3">
-        <v>245700</v>
+        <v>249300</v>
       </c>
       <c r="I9" s="3">
-        <v>172800</v>
+        <v>247400</v>
       </c>
       <c r="J9" s="3">
+        <v>174000</v>
+      </c>
+      <c r="K9" s="3">
         <v>136300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>207900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>228500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>226200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>210600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>320600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>293300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>368100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>257200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>229000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>217500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>160900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>173000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>151500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>164000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>166700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>182200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>165500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>154200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>137800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>167000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>125700</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>137400</v>
+        <v>188600</v>
       </c>
       <c r="E10" s="3">
+        <v>138400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>125600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>145100</v>
+      </c>
+      <c r="H10" s="3">
         <v>124700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
+        <v>88000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>64100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>167400</v>
+      </c>
+      <c r="L10" s="3">
+        <v>214200</v>
+      </c>
+      <c r="M10" s="3">
+        <v>236200</v>
+      </c>
+      <c r="N10" s="3">
+        <v>196600</v>
+      </c>
+      <c r="O10" s="3">
+        <v>211600</v>
+      </c>
+      <c r="P10" s="3">
         <v>144100</v>
       </c>
-      <c r="G10" s="3">
-        <v>123900</v>
-      </c>
-      <c r="H10" s="3">
-        <v>87400</v>
-      </c>
-      <c r="I10" s="3">
-        <v>63600</v>
-      </c>
-      <c r="J10" s="3">
-        <v>167400</v>
-      </c>
-      <c r="K10" s="3">
-        <v>214200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>236200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>196600</v>
-      </c>
-      <c r="N10" s="3">
-        <v>211600</v>
-      </c>
-      <c r="O10" s="3">
-        <v>144100</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>142600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>26300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>227500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>261900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>171400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>109000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>197200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>107400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>121500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>64800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>54300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>50100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>41200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>39400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>35200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>16800</v>
+        <v>17600</v>
       </c>
       <c r="E12" s="3">
-        <v>17900</v>
+        <v>16900</v>
       </c>
       <c r="F12" s="3">
-        <v>18700</v>
+        <v>18000</v>
       </c>
       <c r="G12" s="3">
-        <v>19400</v>
+        <v>18900</v>
       </c>
       <c r="H12" s="3">
-        <v>21300</v>
+        <v>19500</v>
       </c>
       <c r="I12" s="3">
-        <v>21100</v>
+        <v>21500</v>
       </c>
       <c r="J12" s="3">
+        <v>21200</v>
+      </c>
+      <c r="K12" s="3">
         <v>22600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>18600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>15600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>11600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>11000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>19900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1285,32 +1305,32 @@
       <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" s="3">
         <v>4700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1322,23 +1342,23 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1500</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>700</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="3">
         <v>100</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1346,13 +1366,16 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>800</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>377100</v>
+        <v>385800</v>
       </c>
       <c r="E17" s="3">
-        <v>379200</v>
+        <v>379700</v>
       </c>
       <c r="F17" s="3">
-        <v>367700</v>
+        <v>381800</v>
       </c>
       <c r="G17" s="3">
-        <v>340000</v>
+        <v>370200</v>
       </c>
       <c r="H17" s="3">
-        <v>348600</v>
+        <v>342300</v>
       </c>
       <c r="I17" s="3">
-        <v>259800</v>
+        <v>351000</v>
       </c>
       <c r="J17" s="3">
+        <v>261600</v>
+      </c>
+      <c r="K17" s="3">
         <v>220400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>310600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>334500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>312400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>293800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>411400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>378100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>443700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>371300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>343000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>296900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>218100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>227900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>193700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>205600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>199500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>206600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>199300</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD17" s="3">
         <v>163100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>195600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>147300</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>44800</v>
+        <v>102000</v>
       </c>
       <c r="E18" s="3">
-        <v>32700</v>
+        <v>45100</v>
       </c>
       <c r="F18" s="3">
-        <v>53500</v>
+        <v>32900</v>
       </c>
       <c r="G18" s="3">
-        <v>31400</v>
+        <v>53900</v>
       </c>
       <c r="H18" s="3">
-        <v>-15400</v>
+        <v>31700</v>
       </c>
       <c r="I18" s="3">
-        <v>-23300</v>
+        <v>-15600</v>
       </c>
       <c r="J18" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="K18" s="3">
         <v>83200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>111500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>130100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>110300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>128400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>53400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>57800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-49300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>113400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>147900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>92000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>51800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>142200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>65200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>79800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>32000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>29900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16300</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD18" s="3">
         <v>14100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>6500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,97 +1714,101 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>15500</v>
+        <v>-34400</v>
       </c>
       <c r="E20" s="3">
-        <v>22800</v>
+        <v>15600</v>
       </c>
       <c r="F20" s="3">
-        <v>-1900</v>
+        <v>23000</v>
       </c>
       <c r="G20" s="3">
-        <v>16400</v>
+        <v>-2000</v>
       </c>
       <c r="H20" s="3">
-        <v>44100</v>
+        <v>16500</v>
       </c>
       <c r="I20" s="3">
-        <v>37300</v>
+        <v>44400</v>
       </c>
       <c r="J20" s="3">
+        <v>37500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-41400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-13800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-44300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-77400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-18900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-17300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>22600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>26100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>41600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>9000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7600</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD20" s="3">
         <v>2100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1841,26 +1878,29 @@
       <c r="Y21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA21" s="3">
         <v>33000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE21" s="3">
         <v>6600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1897,8 +1937,8 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>10</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>10</v>
@@ -1915,219 +1955,228 @@
       <c r="T22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>60300</v>
+        <v>67600</v>
       </c>
       <c r="E23" s="3">
-        <v>55500</v>
+        <v>60700</v>
       </c>
       <c r="F23" s="3">
-        <v>51600</v>
+        <v>55900</v>
       </c>
       <c r="G23" s="3">
-        <v>47800</v>
+        <v>51900</v>
       </c>
       <c r="H23" s="3">
-        <v>28700</v>
+        <v>48200</v>
       </c>
       <c r="I23" s="3">
-        <v>13900</v>
+        <v>28900</v>
       </c>
       <c r="J23" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K23" s="3">
         <v>41800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>97600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>133300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>121000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>84100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>57400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>73000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-126700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>94500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>130600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>114600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>77600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>183200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>73000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>78200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>31500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>31100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>13100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E24" s="3">
         <v>11200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10300</v>
       </c>
-      <c r="F24" s="3">
-        <v>10000</v>
-      </c>
       <c r="G24" s="3">
+        <v>10100</v>
+      </c>
+      <c r="H24" s="3">
         <v>9800</v>
       </c>
-      <c r="H24" s="3">
-        <v>5500</v>
-      </c>
       <c r="I24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J24" s="3">
         <v>2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>18900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-19700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>19100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>30700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>16200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>10300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4900</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>4700</v>
       </c>
       <c r="AE24" s="3">
         <v>4700</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>49100</v>
+        <v>51500</v>
       </c>
       <c r="E26" s="3">
-        <v>45200</v>
+        <v>49500</v>
       </c>
       <c r="F26" s="3">
-        <v>41600</v>
+        <v>45500</v>
       </c>
       <c r="G26" s="3">
-        <v>38100</v>
+        <v>41900</v>
       </c>
       <c r="H26" s="3">
-        <v>23100</v>
+        <v>38300</v>
       </c>
       <c r="I26" s="3">
+        <v>23300</v>
+      </c>
+      <c r="J26" s="3">
         <v>11300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>35300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>82600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>111800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>102100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>70900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>50800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>61700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-107000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>79700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>111500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>98000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>64500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>152400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>62600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>92900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>25500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>14900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>10100</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD26" s="3">
         <v>8200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>49100</v>
+        <v>51500</v>
       </c>
       <c r="E27" s="3">
-        <v>45200</v>
+        <v>49500</v>
       </c>
       <c r="F27" s="3">
-        <v>41600</v>
+        <v>45500</v>
       </c>
       <c r="G27" s="3">
-        <v>38000</v>
+        <v>41900</v>
       </c>
       <c r="H27" s="3">
-        <v>22800</v>
+        <v>38300</v>
       </c>
       <c r="I27" s="3">
-        <v>10800</v>
+        <v>22900</v>
       </c>
       <c r="J27" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K27" s="3">
         <v>35300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>82500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>111800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>102200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>70900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>50800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>61700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-107000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>79700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>111500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>98000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>64500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>152400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>62600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>92900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>25500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD27" s="3">
         <v>800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15500</v>
+        <v>34400</v>
       </c>
       <c r="E32" s="3">
-        <v>-22800</v>
+        <v>-15600</v>
       </c>
       <c r="F32" s="3">
-        <v>1900</v>
+        <v>-23000</v>
       </c>
       <c r="G32" s="3">
-        <v>-16400</v>
+        <v>2000</v>
       </c>
       <c r="H32" s="3">
-        <v>-44100</v>
+        <v>-16500</v>
       </c>
       <c r="I32" s="3">
-        <v>-37300</v>
+        <v>-44400</v>
       </c>
       <c r="J32" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="K32" s="3">
         <v>41400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>13800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>44300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>77400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>18900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>17300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-22600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-26100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-41600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-9000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>49100</v>
+        <v>51500</v>
       </c>
       <c r="E33" s="3">
-        <v>45200</v>
+        <v>49500</v>
       </c>
       <c r="F33" s="3">
-        <v>41600</v>
+        <v>45500</v>
       </c>
       <c r="G33" s="3">
-        <v>38000</v>
+        <v>41900</v>
       </c>
       <c r="H33" s="3">
-        <v>22800</v>
+        <v>38300</v>
       </c>
       <c r="I33" s="3">
-        <v>10800</v>
+        <v>22900</v>
       </c>
       <c r="J33" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K33" s="3">
         <v>35300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>82500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>111800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>102200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>70900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>50800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>61700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-107000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>79700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>111500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>98000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>64500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>152400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>62600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>92900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>25500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>800</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD33" s="3">
         <v>800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>49100</v>
+        <v>51500</v>
       </c>
       <c r="E35" s="3">
-        <v>45200</v>
+        <v>49500</v>
       </c>
       <c r="F35" s="3">
-        <v>41600</v>
+        <v>45500</v>
       </c>
       <c r="G35" s="3">
-        <v>38000</v>
+        <v>41900</v>
       </c>
       <c r="H35" s="3">
-        <v>22800</v>
+        <v>38300</v>
       </c>
       <c r="I35" s="3">
-        <v>10800</v>
+        <v>22900</v>
       </c>
       <c r="J35" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K35" s="3">
         <v>35300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>82500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>111800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>102200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>70900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>50800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>61700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-107000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>79700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>111500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>98000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>64500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>152400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>62600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>92900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>25500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>800</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD35" s="3">
         <v>800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>362800</v>
+        <v>351300</v>
       </c>
       <c r="E41" s="3">
-        <v>316500</v>
+        <v>365300</v>
       </c>
       <c r="F41" s="3">
-        <v>206300</v>
+        <v>318600</v>
       </c>
       <c r="G41" s="3">
-        <v>291100</v>
+        <v>207700</v>
       </c>
       <c r="H41" s="3">
-        <v>284500</v>
+        <v>293100</v>
       </c>
       <c r="I41" s="3">
-        <v>318100</v>
+        <v>286500</v>
       </c>
       <c r="J41" s="3">
+        <v>320200</v>
+      </c>
+      <c r="K41" s="3">
         <v>367900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>361900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>338900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>335900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>217700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>234800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>171600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>204100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>321100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>431100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>165300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>204100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>166800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>61700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>61600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>88000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>167200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>74900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>145700</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3365,11 +3455,11 @@
       <c r="E42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F42" s="3">
-        <v>37300</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="F42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="3">
+        <v>37500</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>10</v>
@@ -3386,8 +3476,8 @@
       <c r="L42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -3443,590 +3533,611 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1343300</v>
+        <v>1367100</v>
       </c>
       <c r="E43" s="3">
-        <v>1347900</v>
+        <v>1352400</v>
       </c>
       <c r="F43" s="3">
-        <v>1422000</v>
+        <v>1357100</v>
       </c>
       <c r="G43" s="3">
-        <v>1405700</v>
+        <v>1431700</v>
       </c>
       <c r="H43" s="3">
-        <v>1290600</v>
+        <v>1415300</v>
       </c>
       <c r="I43" s="3">
-        <v>1158300</v>
+        <v>1299400</v>
       </c>
       <c r="J43" s="3">
+        <v>1166100</v>
+      </c>
+      <c r="K43" s="3">
         <v>1183700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1143300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1213000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1206900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1370400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1473600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1384300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1357000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1226000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1001000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>900300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>875300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>953400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>957000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1390300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1719200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1509000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1421400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1287700</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7600</v>
       </c>
-      <c r="E44" s="3">
-        <v>7000</v>
-      </c>
       <c r="F44" s="3">
-        <v>7400</v>
+        <v>7100</v>
       </c>
       <c r="G44" s="3">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="H44" s="3">
-        <v>9300</v>
+        <v>12100</v>
       </c>
       <c r="I44" s="3">
-        <v>7800</v>
+        <v>9400</v>
       </c>
       <c r="J44" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K44" s="3">
         <v>6600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>16400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>21400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>15800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>10600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>15100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>18500</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE44" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>859100</v>
+        <v>856500</v>
       </c>
       <c r="E45" s="3">
-        <v>1020000</v>
+        <v>864900</v>
       </c>
       <c r="F45" s="3">
-        <v>782300</v>
+        <v>1027000</v>
       </c>
       <c r="G45" s="3">
-        <v>746900</v>
+        <v>787600</v>
       </c>
       <c r="H45" s="3">
-        <v>779500</v>
+        <v>752000</v>
       </c>
       <c r="I45" s="3">
-        <v>817300</v>
+        <v>784900</v>
       </c>
       <c r="J45" s="3">
+        <v>822800</v>
+      </c>
+      <c r="K45" s="3">
         <v>741600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>802100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>718700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>709200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>690800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1001300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1110800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1018200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>978100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>710400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>581500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>421600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>368100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>409800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>286300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>266700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>199200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>111500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>70400</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2572700</v>
+        <v>2582900</v>
       </c>
       <c r="E46" s="3">
-        <v>2691500</v>
+        <v>2590300</v>
       </c>
       <c r="F46" s="3">
-        <v>2455400</v>
+        <v>2709800</v>
       </c>
       <c r="G46" s="3">
-        <v>2455700</v>
+        <v>2472100</v>
       </c>
       <c r="H46" s="3">
-        <v>2364000</v>
+        <v>2472400</v>
       </c>
       <c r="I46" s="3">
-        <v>2301400</v>
+        <v>2380100</v>
       </c>
       <c r="J46" s="3">
+        <v>2317100</v>
+      </c>
+      <c r="K46" s="3">
         <v>2299800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2314800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2277100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2261600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2285400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2718400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2675000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2588000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2541600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2163900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1662800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1509400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1496600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1441900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1748800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2087400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1890500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1626700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1522300</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>204700</v>
+        <v>185200</v>
       </c>
       <c r="E47" s="3">
-        <v>196600</v>
+        <v>206100</v>
       </c>
       <c r="F47" s="3">
-        <v>195200</v>
+        <v>198000</v>
       </c>
       <c r="G47" s="3">
-        <v>195500</v>
+        <v>196500</v>
       </c>
       <c r="H47" s="3">
-        <v>184600</v>
+        <v>196800</v>
       </c>
       <c r="I47" s="3">
-        <v>143900</v>
+        <v>185900</v>
       </c>
       <c r="J47" s="3">
+        <v>144900</v>
+      </c>
+      <c r="K47" s="3">
         <v>145900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>168900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>183700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>194400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>198700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>197200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>212500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>249100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>297900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>310000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>258300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>248900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>272600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>253800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>314900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>349900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>268400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>218800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>194900</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>53200</v>
+        <v>59500</v>
       </c>
       <c r="E48" s="3">
-        <v>45200</v>
+        <v>53600</v>
       </c>
       <c r="F48" s="3">
-        <v>39300</v>
+        <v>45500</v>
       </c>
       <c r="G48" s="3">
-        <v>33500</v>
+        <v>39600</v>
       </c>
       <c r="H48" s="3">
-        <v>29900</v>
+        <v>33700</v>
       </c>
       <c r="I48" s="3">
-        <v>29600</v>
+        <v>30100</v>
       </c>
       <c r="J48" s="3">
+        <v>29800</v>
+      </c>
+      <c r="K48" s="3">
         <v>27000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8700</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>126300</v>
+        <v>125900</v>
       </c>
       <c r="E49" s="3">
-        <v>127500</v>
+        <v>127100</v>
       </c>
       <c r="F49" s="3">
-        <v>128600</v>
+        <v>128300</v>
       </c>
       <c r="G49" s="3">
-        <v>129800</v>
+        <v>129500</v>
       </c>
       <c r="H49" s="3">
-        <v>131000</v>
+        <v>130700</v>
       </c>
       <c r="I49" s="3">
-        <v>132200</v>
+        <v>131900</v>
       </c>
       <c r="J49" s="3">
+        <v>133100</v>
+      </c>
+      <c r="K49" s="3">
         <v>133400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>138500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>139800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>142500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>139300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>148700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>150000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>161900</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>10</v>
       </c>
@@ -4039,8 +4150,8 @@
       <c r="V49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>342000</v>
+        <v>342300</v>
       </c>
       <c r="E52" s="3">
+        <v>344300</v>
+      </c>
+      <c r="F52" s="3">
+        <v>337900</v>
+      </c>
+      <c r="G52" s="3">
+        <v>327900</v>
+      </c>
+      <c r="H52" s="3">
         <v>335700</v>
       </c>
-      <c r="F52" s="3">
-        <v>325700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>333400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>337000</v>
-      </c>
       <c r="I52" s="3">
-        <v>318500</v>
+        <v>339300</v>
       </c>
       <c r="J52" s="3">
+        <v>320600</v>
+      </c>
+      <c r="K52" s="3">
         <v>297300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>279600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>241400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>202900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>191200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>183300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>176700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>177400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>108200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>98300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>67800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>54000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>29900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>42900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>38800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>18600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>17700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>12400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8400</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3298900</v>
+        <v>3295900</v>
       </c>
       <c r="E54" s="3">
-        <v>3396400</v>
+        <v>3321400</v>
       </c>
       <c r="F54" s="3">
-        <v>3144200</v>
+        <v>3419500</v>
       </c>
       <c r="G54" s="3">
-        <v>3148000</v>
+        <v>3165600</v>
       </c>
       <c r="H54" s="3">
-        <v>3046500</v>
+        <v>3169400</v>
       </c>
       <c r="I54" s="3">
-        <v>2925600</v>
+        <v>3067300</v>
       </c>
       <c r="J54" s="3">
+        <v>2945600</v>
+      </c>
+      <c r="K54" s="3">
         <v>2903300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2924100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2860800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2819200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2832000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3262900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3229800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3192300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2962000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2586100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2003200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1826400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1811100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1749600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2113200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2466200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2186000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1866600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1734300</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,516 +4707,532 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>5500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4600</v>
       </c>
-      <c r="H57" s="3">
-        <v>8300</v>
-      </c>
       <c r="I57" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J57" s="3">
         <v>3500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>31100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>31800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>38800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>21900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>19700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>29800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>27100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>18600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>29400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11700</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>800500</v>
+        <v>757200</v>
       </c>
       <c r="E58" s="3">
-        <v>1079200</v>
+        <v>806000</v>
       </c>
       <c r="F58" s="3">
-        <v>1051700</v>
+        <v>1086600</v>
       </c>
       <c r="G58" s="3">
-        <v>1002000</v>
+        <v>1058900</v>
       </c>
       <c r="H58" s="3">
-        <v>644200</v>
+        <v>1008800</v>
       </c>
       <c r="I58" s="3">
-        <v>567700</v>
+        <v>648600</v>
       </c>
       <c r="J58" s="3">
+        <v>571500</v>
+      </c>
+      <c r="K58" s="3">
         <v>676700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>699600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>755800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>912700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>906600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1003500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1045300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1007500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>882800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>701900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>657800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>605900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>738400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>951600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1402200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1893600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1587100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1618800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1541700</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>828900</v>
+        <v>994700</v>
       </c>
       <c r="E59" s="3">
-        <v>743200</v>
+        <v>834500</v>
       </c>
       <c r="F59" s="3">
-        <v>668200</v>
+        <v>748300</v>
       </c>
       <c r="G59" s="3">
-        <v>665900</v>
+        <v>672700</v>
       </c>
       <c r="H59" s="3">
-        <v>661200</v>
+        <v>670400</v>
       </c>
       <c r="I59" s="3">
-        <v>691700</v>
+        <v>665700</v>
       </c>
       <c r="J59" s="3">
+        <v>696400</v>
+      </c>
+      <c r="K59" s="3">
         <v>727700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>721300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>719300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>680900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>760500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1045100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1055700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1077900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>595500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>535200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>442300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>415200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>406500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>321700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>293700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>242300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>292200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>186800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>158000</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1634900</v>
+        <v>1753900</v>
       </c>
       <c r="E60" s="3">
-        <v>1827500</v>
+        <v>1646000</v>
       </c>
       <c r="F60" s="3">
-        <v>1723500</v>
+        <v>1839900</v>
       </c>
       <c r="G60" s="3">
-        <v>1672400</v>
+        <v>1735200</v>
       </c>
       <c r="H60" s="3">
-        <v>1313700</v>
+        <v>1683800</v>
       </c>
       <c r="I60" s="3">
-        <v>1262800</v>
+        <v>1322600</v>
       </c>
       <c r="J60" s="3">
+        <v>1271400</v>
+      </c>
+      <c r="K60" s="3">
         <v>1406600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1423600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1480400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1599700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1673100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2058300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2109800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2100300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1509400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1269000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1138900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1043000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1164600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1303200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1723000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2154400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1908700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1815300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1711400</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>355100</v>
+        <v>166900</v>
       </c>
       <c r="E61" s="3">
-        <v>304500</v>
+        <v>357500</v>
       </c>
       <c r="F61" s="3">
-        <v>205000</v>
+        <v>306600</v>
       </c>
       <c r="G61" s="3">
-        <v>299400</v>
+        <v>206400</v>
       </c>
       <c r="H61" s="3">
-        <v>574700</v>
+        <v>301400</v>
       </c>
       <c r="I61" s="3">
-        <v>504300</v>
+        <v>578700</v>
       </c>
       <c r="J61" s="3">
+        <v>507700</v>
+      </c>
+      <c r="K61" s="3">
         <v>356200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>371700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>358500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>308400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>382200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>469300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>440800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>441600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>384400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>338000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>32100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>22900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>52200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>47300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>35300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>24800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>19900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>14600</v>
+        <v>16600</v>
       </c>
       <c r="E62" s="3">
-        <v>19800</v>
+        <v>14700</v>
       </c>
       <c r="F62" s="3">
-        <v>21500</v>
+        <v>20000</v>
       </c>
       <c r="G62" s="3">
-        <v>22100</v>
+        <v>21600</v>
       </c>
       <c r="H62" s="3">
+        <v>22300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>29500</v>
+      </c>
+      <c r="J62" s="3">
         <v>29300</v>
       </c>
-      <c r="I62" s="3">
-        <v>29100</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>52000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>51700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>42600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>33400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>27200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5102,8 +5248,8 @@
       <c r="AB62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2004600</v>
+        <v>1937400</v>
       </c>
       <c r="E66" s="3">
-        <v>2151800</v>
+        <v>2018300</v>
       </c>
       <c r="F66" s="3">
-        <v>1950000</v>
+        <v>2166400</v>
       </c>
       <c r="G66" s="3">
-        <v>1999600</v>
+        <v>1963200</v>
       </c>
       <c r="H66" s="3">
-        <v>1923400</v>
+        <v>2013200</v>
       </c>
       <c r="I66" s="3">
-        <v>1804900</v>
+        <v>1936500</v>
       </c>
       <c r="J66" s="3">
+        <v>1817100</v>
+      </c>
+      <c r="K66" s="3">
         <v>1794800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1827100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1852900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1921300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2067700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2537800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2562200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2551900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1945800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1658700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1185500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1108400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1214700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1355400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1770300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2189700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1933500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1835100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1716400</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5753,22 +5921,25 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>100100</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>97600</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>911300</v>
+        <v>969100</v>
       </c>
       <c r="E72" s="3">
-        <v>862200</v>
+        <v>917500</v>
       </c>
       <c r="F72" s="3">
-        <v>817000</v>
+        <v>868100</v>
       </c>
       <c r="G72" s="3">
-        <v>775400</v>
+        <v>822600</v>
       </c>
       <c r="H72" s="3">
-        <v>737300</v>
+        <v>780700</v>
       </c>
       <c r="I72" s="3">
-        <v>714600</v>
+        <v>742400</v>
       </c>
       <c r="J72" s="3">
+        <v>719500</v>
+      </c>
+      <c r="K72" s="3">
         <v>703800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>688200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>605600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>499000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>384600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>332100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>281300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>235000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>629300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>549500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>443800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>361300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>260300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>74600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>30400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-35600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-58600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-72800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-82900</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1294300</v>
+        <v>1358500</v>
       </c>
       <c r="E76" s="3">
-        <v>1244600</v>
+        <v>1303100</v>
       </c>
       <c r="F76" s="3">
-        <v>1194200</v>
+        <v>1253100</v>
       </c>
       <c r="G76" s="3">
-        <v>1148400</v>
+        <v>1202300</v>
       </c>
       <c r="H76" s="3">
-        <v>1123200</v>
+        <v>1156200</v>
       </c>
       <c r="I76" s="3">
-        <v>1120800</v>
+        <v>1130800</v>
       </c>
       <c r="J76" s="3">
+        <v>1128400</v>
+      </c>
+      <c r="K76" s="3">
         <v>1108500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1097000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1007800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>898000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>764300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>725000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>667500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>640500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1016200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>927400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>817700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>718000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>596400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>394200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>342900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>276500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>252500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-68600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-79700</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>49100</v>
+        <v>51500</v>
       </c>
       <c r="E81" s="3">
-        <v>45200</v>
+        <v>49500</v>
       </c>
       <c r="F81" s="3">
-        <v>41600</v>
+        <v>45500</v>
       </c>
       <c r="G81" s="3">
-        <v>38000</v>
+        <v>41900</v>
       </c>
       <c r="H81" s="3">
-        <v>22800</v>
+        <v>38300</v>
       </c>
       <c r="I81" s="3">
-        <v>10800</v>
+        <v>22900</v>
       </c>
       <c r="J81" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K81" s="3">
         <v>35300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>82500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>111800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>102200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>70900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>50800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>61700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-107000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>79700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>111500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>98000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>64500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>152400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>62600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>92900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>25500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>800</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD81" s="3">
         <v>800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6678,11 +6877,11 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
         <v>800</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>10</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7212,11 +7429,11 @@
         <v>0</v>
       </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>99300</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>10</v>
       </c>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7334,11 +7555,11 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-800</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>10</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7601,11 +7831,11 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-187300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>10</v>
       </c>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8079,11 +8325,11 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>180500</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>10</v>
       </c>
@@ -8096,8 +8342,11 @@
       <c r="AE100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8168,11 +8417,11 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB101" s="3" t="s">
         <v>10</v>
       </c>
@@ -8185,8 +8434,11 @@
       <c r="AE101" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8257,11 +8509,11 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>92300</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>10</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>10</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>LX</t>
   </si>
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>487800</v>
+        <v>447900</v>
       </c>
       <c r="E8" s="3">
-        <v>424800</v>
+        <v>484900</v>
       </c>
       <c r="F8" s="3">
-        <v>414700</v>
+        <v>484800</v>
       </c>
       <c r="G8" s="3">
-        <v>424100</v>
+        <v>422200</v>
       </c>
       <c r="H8" s="3">
-        <v>374000</v>
+        <v>412100</v>
       </c>
       <c r="I8" s="3">
+        <v>421400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>371700</v>
+      </c>
+      <c r="K8" s="3">
         <v>335400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>238100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>303700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>422000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>464700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>422800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>422200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>464800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>435900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>394400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>484700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>490900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>388900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>269900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>370200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>258900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>285400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>231500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>236500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>215600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>195500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>177200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>202100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>299300</v>
+        <v>282600</v>
       </c>
       <c r="E9" s="3">
-        <v>286400</v>
+        <v>311000</v>
       </c>
       <c r="F9" s="3">
-        <v>289100</v>
+        <v>297400</v>
       </c>
       <c r="G9" s="3">
-        <v>279000</v>
+        <v>284700</v>
       </c>
       <c r="H9" s="3">
-        <v>249300</v>
+        <v>287300</v>
       </c>
       <c r="I9" s="3">
+        <v>277300</v>
+      </c>
+      <c r="J9" s="3">
+        <v>247700</v>
+      </c>
+      <c r="K9" s="3">
         <v>247400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>174000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>136300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>207900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>228500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>226200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>210600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>320600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>293300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>368100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>257200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>229000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>217500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>160900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>173000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>151500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>164000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>166700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>182200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>165500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>154200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>137800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>167000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>125700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>188600</v>
+        <v>165300</v>
       </c>
       <c r="E10" s="3">
-        <v>138400</v>
+        <v>173800</v>
       </c>
       <c r="F10" s="3">
-        <v>125600</v>
+        <v>187400</v>
       </c>
       <c r="G10" s="3">
-        <v>145100</v>
+        <v>137500</v>
       </c>
       <c r="H10" s="3">
-        <v>124700</v>
+        <v>124800</v>
       </c>
       <c r="I10" s="3">
+        <v>144200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>124000</v>
+      </c>
+      <c r="K10" s="3">
         <v>88000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>64100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>167400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>214200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>236200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>196600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>211600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>144100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>142600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>26300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>227500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>261900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>171400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>109000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>197200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>107400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>121500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>64800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>54300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>50100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>41200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>39400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>35200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1123,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>17600</v>
+        <v>18600</v>
       </c>
       <c r="E12" s="3">
-        <v>16900</v>
+        <v>18800</v>
       </c>
       <c r="F12" s="3">
-        <v>18000</v>
+        <v>17500</v>
       </c>
       <c r="G12" s="3">
-        <v>18900</v>
+        <v>16800</v>
       </c>
       <c r="H12" s="3">
-        <v>19500</v>
+        <v>17900</v>
       </c>
       <c r="I12" s="3">
+        <v>18700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>19400</v>
+      </c>
+      <c r="K12" s="3">
         <v>21500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>21200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>22600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>18600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>18500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>17800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>13200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>17400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>19800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>19900</v>
-      </c>
-      <c r="S12" s="3">
-        <v>15600</v>
-      </c>
-      <c r="T12" s="3">
-        <v>18600</v>
       </c>
       <c r="U12" s="3">
         <v>15600</v>
       </c>
       <c r="V12" s="3">
+        <v>18600</v>
+      </c>
+      <c r="W12" s="3">
+        <v>15600</v>
+      </c>
+      <c r="X12" s="3">
         <v>14300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>11600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>13100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>11000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>9800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>19900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>10000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>8500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>6400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>6600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,61 +1315,67 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>5200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1345,37 +1384,43 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>700</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>800</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>385800</v>
+        <v>371300</v>
       </c>
       <c r="E17" s="3">
-        <v>379700</v>
+        <v>404100</v>
       </c>
       <c r="F17" s="3">
-        <v>381800</v>
+        <v>383400</v>
       </c>
       <c r="G17" s="3">
-        <v>370200</v>
+        <v>377400</v>
       </c>
       <c r="H17" s="3">
-        <v>342300</v>
+        <v>379400</v>
       </c>
       <c r="I17" s="3">
+        <v>367900</v>
+      </c>
+      <c r="J17" s="3">
+        <v>340200</v>
+      </c>
+      <c r="K17" s="3">
         <v>351000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>261600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>220400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>310600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>334500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>312400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>293800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>411400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>378100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>443700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>371300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>343000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>296900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>218100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>227900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>193700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>205600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>199500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>206600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>199300</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF17" s="3">
         <v>163100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>195600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>147300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>102000</v>
+        <v>76600</v>
       </c>
       <c r="E18" s="3">
-        <v>45100</v>
+        <v>80700</v>
       </c>
       <c r="F18" s="3">
-        <v>32900</v>
+        <v>101300</v>
       </c>
       <c r="G18" s="3">
-        <v>53900</v>
+        <v>44800</v>
       </c>
       <c r="H18" s="3">
-        <v>31700</v>
+        <v>32700</v>
       </c>
       <c r="I18" s="3">
+        <v>53600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>31500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-15600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-23500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>83200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>111500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>130100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>110300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>128400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>53400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>57800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-49300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>113400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>147900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>92000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>51800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>142200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>65200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>79800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>32000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>29900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>16300</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF18" s="3">
         <v>14100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>6500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,100 +1780,108 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-34400</v>
+        <v>-41300</v>
       </c>
       <c r="E20" s="3">
-        <v>15600</v>
+        <v>-80400</v>
       </c>
       <c r="F20" s="3">
-        <v>23000</v>
+        <v>-34200</v>
       </c>
       <c r="G20" s="3">
-        <v>-2000</v>
+        <v>15500</v>
       </c>
       <c r="H20" s="3">
-        <v>16500</v>
+        <v>22800</v>
       </c>
       <c r="I20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J20" s="3">
+        <v>16400</v>
+      </c>
+      <c r="K20" s="3">
         <v>44400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>37500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-41400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-13800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>3200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>10600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-44300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>4000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>15300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-77400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-18900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-17300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>22600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>26100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>41600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>9000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>2300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>7600</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF20" s="3">
         <v>2100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1881,26 +1954,32 @@
       <c r="Z21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC21" s="3">
         <v>33000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG21" s="3">
         <v>6600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1940,11 +2019,11 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>10</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>10</v>
@@ -1958,225 +2037,243 @@
       <c r="U22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>1000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>1100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>3600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>3300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>3200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>3000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>67600</v>
+        <v>35200</v>
       </c>
       <c r="E23" s="3">
-        <v>60700</v>
+        <v>300</v>
       </c>
       <c r="F23" s="3">
-        <v>55900</v>
+        <v>67200</v>
       </c>
       <c r="G23" s="3">
-        <v>51900</v>
+        <v>60300</v>
       </c>
       <c r="H23" s="3">
-        <v>48200</v>
+        <v>55500</v>
       </c>
       <c r="I23" s="3">
+        <v>51600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>47900</v>
+      </c>
+      <c r="K23" s="3">
         <v>28900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>14000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>41800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>97600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>133300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>121000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>84100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>57400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>73000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-126700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>94500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>130600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>114600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>77600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>183200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>73000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>78200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>31500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>31100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>20400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>5600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>13100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>16100</v>
+        <v>7400</v>
       </c>
       <c r="E24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="G24" s="3">
         <v>11200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>10300</v>
       </c>
-      <c r="G24" s="3">
-        <v>10100</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J24" s="3">
         <v>9800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>5600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>6500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>15100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>21500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>18900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>13100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>6600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>11300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-19700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>14800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>19100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>16600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>13000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>30700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>10500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-14700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>5900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>16200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>10300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>3300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>4900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>4700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>51500</v>
+        <v>27900</v>
       </c>
       <c r="E26" s="3">
-        <v>49500</v>
+        <v>1700</v>
       </c>
       <c r="F26" s="3">
-        <v>45500</v>
+        <v>51200</v>
       </c>
       <c r="G26" s="3">
-        <v>41900</v>
+        <v>49100</v>
       </c>
       <c r="H26" s="3">
-        <v>38300</v>
+        <v>45200</v>
       </c>
       <c r="I26" s="3">
+        <v>41600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>38100</v>
+      </c>
+      <c r="K26" s="3">
         <v>23300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>11300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>35300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>82600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>111800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>102100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>70900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>50800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>61700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-107000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>79700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>111500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>98000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>64500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>152400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>62600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>92900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>25500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>14900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>10100</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF26" s="3">
         <v>8200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>51500</v>
+        <v>27900</v>
       </c>
       <c r="E27" s="3">
-        <v>49500</v>
+        <v>1700</v>
       </c>
       <c r="F27" s="3">
-        <v>45500</v>
+        <v>51200</v>
       </c>
       <c r="G27" s="3">
-        <v>41900</v>
+        <v>49100</v>
       </c>
       <c r="H27" s="3">
-        <v>38300</v>
+        <v>45200</v>
       </c>
       <c r="I27" s="3">
+        <v>41600</v>
+      </c>
+      <c r="J27" s="3">
+        <v>38100</v>
+      </c>
+      <c r="K27" s="3">
         <v>22900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>10900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>35300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>82500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>111800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>102200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>70900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>50800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>61700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-107000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>79700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>111500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>98000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>64500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>152400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>62600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>92900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>25500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>3200</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>800</v>
-      </c>
-      <c r="AC27" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD27" s="3">
         <v>800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>34400</v>
+        <v>41300</v>
       </c>
       <c r="E32" s="3">
-        <v>-15600</v>
+        <v>80400</v>
       </c>
       <c r="F32" s="3">
-        <v>-23000</v>
+        <v>34200</v>
       </c>
       <c r="G32" s="3">
-        <v>2000</v>
+        <v>-15500</v>
       </c>
       <c r="H32" s="3">
-        <v>-16500</v>
+        <v>-22800</v>
       </c>
       <c r="I32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-44400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-37500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>41400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>13800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-3200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-10600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>44300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-15300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>77400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>18900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>17300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-22600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-26100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-41600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>51500</v>
+        <v>27900</v>
       </c>
       <c r="E33" s="3">
-        <v>49500</v>
+        <v>1700</v>
       </c>
       <c r="F33" s="3">
-        <v>45500</v>
+        <v>51200</v>
       </c>
       <c r="G33" s="3">
-        <v>41900</v>
+        <v>49100</v>
       </c>
       <c r="H33" s="3">
-        <v>38300</v>
+        <v>45200</v>
       </c>
       <c r="I33" s="3">
+        <v>41600</v>
+      </c>
+      <c r="J33" s="3">
+        <v>38100</v>
+      </c>
+      <c r="K33" s="3">
         <v>22900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>10900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>35300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>82500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>111800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>102200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>70900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>50800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>61700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-107000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>79700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>111500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>98000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>64500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>152400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>62600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>92900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>25500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>3200</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>800</v>
-      </c>
-      <c r="AC33" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD33" s="3">
         <v>800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>51500</v>
+        <v>27900</v>
       </c>
       <c r="E35" s="3">
-        <v>49500</v>
+        <v>1700</v>
       </c>
       <c r="F35" s="3">
-        <v>45500</v>
+        <v>51200</v>
       </c>
       <c r="G35" s="3">
-        <v>41900</v>
+        <v>49100</v>
       </c>
       <c r="H35" s="3">
-        <v>38300</v>
+        <v>45200</v>
       </c>
       <c r="I35" s="3">
+        <v>41600</v>
+      </c>
+      <c r="J35" s="3">
+        <v>38100</v>
+      </c>
+      <c r="K35" s="3">
         <v>22900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>10900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>35300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>82500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>111800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>102200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>70900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>50800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>61700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-107000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>79700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>111500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>98000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>64500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>152400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>62600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>92900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>25500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>3200</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>800</v>
-      </c>
-      <c r="AC35" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD35" s="3">
         <v>800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,120 +3523,128 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>351300</v>
+        <v>267700</v>
       </c>
       <c r="E41" s="3">
-        <v>365300</v>
+        <v>362600</v>
       </c>
       <c r="F41" s="3">
-        <v>318600</v>
+        <v>349100</v>
       </c>
       <c r="G41" s="3">
-        <v>207700</v>
+        <v>363000</v>
       </c>
       <c r="H41" s="3">
-        <v>293100</v>
+        <v>316700</v>
       </c>
       <c r="I41" s="3">
+        <v>206400</v>
+      </c>
+      <c r="J41" s="3">
+        <v>291300</v>
+      </c>
+      <c r="K41" s="3">
         <v>286500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>320200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>367900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>361900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>338900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>335900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>217700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>234800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>171600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>204100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>321100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>431100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>165300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>204100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>166800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>61700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>61600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>88000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>167200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>74900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>145700</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>10</v>
+      <c r="E42" s="3">
+        <v>27600</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="3">
-        <v>37500</v>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>10</v>
+      <c r="I42" s="3">
+        <v>37300</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>10</v>
@@ -3479,11 +3658,11 @@
       <c r="M42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -3536,614 +3715,656 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1367100</v>
+        <v>1479300</v>
       </c>
       <c r="E43" s="3">
-        <v>1352400</v>
+        <v>1390400</v>
       </c>
       <c r="F43" s="3">
-        <v>1357100</v>
+        <v>1358700</v>
       </c>
       <c r="G43" s="3">
-        <v>1431700</v>
+        <v>1344100</v>
       </c>
       <c r="H43" s="3">
-        <v>1415300</v>
+        <v>1348700</v>
       </c>
       <c r="I43" s="3">
+        <v>1422900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1406500</v>
+      </c>
+      <c r="K43" s="3">
         <v>1299400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1166100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1183700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1143300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1213000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1206900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1370400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1473600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1384300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1357000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1226000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1001000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>900300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>875300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>953400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>957000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1390300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1719200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1509000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1421400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1287700</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>8000</v>
+        <v>4100</v>
       </c>
       <c r="E44" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F44" s="3">
+        <v>7900</v>
+      </c>
+      <c r="G44" s="3">
         <v>7600</v>
       </c>
-      <c r="F44" s="3">
-        <v>7100</v>
-      </c>
-      <c r="G44" s="3">
-        <v>7500</v>
-      </c>
       <c r="H44" s="3">
-        <v>12100</v>
+        <v>7000</v>
       </c>
       <c r="I44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="J44" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K44" s="3">
         <v>9400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>7900</v>
-      </c>
-      <c r="K44" s="3">
-        <v>6600</v>
-      </c>
-      <c r="L44" s="3">
-        <v>7500</v>
       </c>
       <c r="M44" s="3">
         <v>6600</v>
       </c>
       <c r="N44" s="3">
-        <v>9700</v>
+        <v>7500</v>
       </c>
       <c r="O44" s="3">
         <v>6600</v>
       </c>
       <c r="P44" s="3">
-        <v>8700</v>
+        <v>9700</v>
       </c>
       <c r="Q44" s="3">
-        <v>8200</v>
+        <v>6600</v>
       </c>
       <c r="R44" s="3">
         <v>8700</v>
       </c>
       <c r="S44" s="3">
+        <v>8200</v>
+      </c>
+      <c r="T44" s="3">
+        <v>8700</v>
+      </c>
+      <c r="U44" s="3">
         <v>16400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>21400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>15800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>8500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>8300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>13300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>10600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>13600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>15100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>18900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>18500</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH44" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>856500</v>
+        <v>881000</v>
       </c>
       <c r="E45" s="3">
-        <v>864900</v>
+        <v>771000</v>
       </c>
       <c r="F45" s="3">
-        <v>1027000</v>
+        <v>851200</v>
       </c>
       <c r="G45" s="3">
-        <v>787600</v>
+        <v>859500</v>
       </c>
       <c r="H45" s="3">
-        <v>752000</v>
+        <v>1020600</v>
       </c>
       <c r="I45" s="3">
+        <v>782700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>747300</v>
+      </c>
+      <c r="K45" s="3">
         <v>784900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>822800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>741600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>802100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>718700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>709200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>690800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1001300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1110800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1018200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>978100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>710400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>581500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>421600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>368100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>409800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>286300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>266700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>199200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>111500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>70400</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2582900</v>
+        <v>2632100</v>
       </c>
       <c r="E46" s="3">
-        <v>2590300</v>
+        <v>2556400</v>
       </c>
       <c r="F46" s="3">
-        <v>2709800</v>
+        <v>2566900</v>
       </c>
       <c r="G46" s="3">
-        <v>2472100</v>
+        <v>2574200</v>
       </c>
       <c r="H46" s="3">
-        <v>2472400</v>
+        <v>2693000</v>
       </c>
       <c r="I46" s="3">
+        <v>2456800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>2457100</v>
+      </c>
+      <c r="K46" s="3">
         <v>2380100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2317100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2299800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2314800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2277100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2261600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2285400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2718400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2675000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2588000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2541600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2163900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1662800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1509400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1496600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1441900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1748800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>2087400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1890500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1626700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1522300</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>185200</v>
+        <v>113200</v>
       </c>
       <c r="E47" s="3">
-        <v>206100</v>
+        <v>145800</v>
       </c>
       <c r="F47" s="3">
-        <v>198000</v>
+        <v>184100</v>
       </c>
       <c r="G47" s="3">
-        <v>196500</v>
+        <v>204800</v>
       </c>
       <c r="H47" s="3">
         <v>196800</v>
       </c>
       <c r="I47" s="3">
+        <v>195300</v>
+      </c>
+      <c r="J47" s="3">
+        <v>195600</v>
+      </c>
+      <c r="K47" s="3">
         <v>185900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>144900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>145900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>168900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>183700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>194400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>198700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>197200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>212500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>249100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>297900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>310000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>258300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>248900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>272600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>253800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>314900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>349900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>268400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>218800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>194900</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>59500</v>
+        <v>66900</v>
       </c>
       <c r="E48" s="3">
-        <v>53600</v>
+        <v>61700</v>
       </c>
       <c r="F48" s="3">
-        <v>45500</v>
+        <v>59100</v>
       </c>
       <c r="G48" s="3">
-        <v>39600</v>
+        <v>53300</v>
       </c>
       <c r="H48" s="3">
-        <v>33700</v>
+        <v>45200</v>
       </c>
       <c r="I48" s="3">
+        <v>39300</v>
+      </c>
+      <c r="J48" s="3">
+        <v>33500</v>
+      </c>
+      <c r="K48" s="3">
         <v>30100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>29800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>27000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>22300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>18800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>17800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>17500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>15300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>15600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>15900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>14300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>13800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>14400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>14100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>12000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>11000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>10700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>10200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>9400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>8600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>8700</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>125900</v>
+        <v>122800</v>
       </c>
       <c r="E49" s="3">
-        <v>127100</v>
+        <v>124000</v>
       </c>
       <c r="F49" s="3">
-        <v>128300</v>
+        <v>125200</v>
       </c>
       <c r="G49" s="3">
-        <v>129500</v>
+        <v>126300</v>
       </c>
       <c r="H49" s="3">
-        <v>130700</v>
+        <v>127500</v>
       </c>
       <c r="I49" s="3">
+        <v>128700</v>
+      </c>
+      <c r="J49" s="3">
+        <v>129900</v>
+      </c>
+      <c r="K49" s="3">
         <v>131900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>133100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>133400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>138500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>139800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>142500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>139300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>148700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>150000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>161900</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>10</v>
       </c>
@@ -4153,11 +4374,11 @@
       <c r="W49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>342300</v>
+        <v>282500</v>
       </c>
       <c r="E52" s="3">
-        <v>344300</v>
+        <v>309300</v>
       </c>
       <c r="F52" s="3">
-        <v>337900</v>
+        <v>340200</v>
       </c>
       <c r="G52" s="3">
-        <v>327900</v>
+        <v>342200</v>
       </c>
       <c r="H52" s="3">
-        <v>335700</v>
+        <v>335900</v>
       </c>
       <c r="I52" s="3">
+        <v>325900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>333600</v>
+      </c>
+      <c r="K52" s="3">
         <v>339300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>320600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>297300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>279600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>241400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>202900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>191200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>183300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>176700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>177400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>108200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>98300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>67800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>54000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>29900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>42900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>38800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>18600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>17700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>12400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>8400</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3295900</v>
+        <v>3217500</v>
       </c>
       <c r="E54" s="3">
-        <v>3321400</v>
+        <v>3197100</v>
       </c>
       <c r="F54" s="3">
-        <v>3419500</v>
+        <v>3275500</v>
       </c>
       <c r="G54" s="3">
-        <v>3165600</v>
+        <v>3300800</v>
       </c>
       <c r="H54" s="3">
-        <v>3169400</v>
+        <v>3398400</v>
       </c>
       <c r="I54" s="3">
+        <v>3146000</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3149800</v>
+      </c>
+      <c r="K54" s="3">
         <v>3067300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2945600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2903300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2924100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2860800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2819200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2832000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3262900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3229800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3192300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2962000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2586100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2003200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1826400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1811100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1749600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2113200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2466200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2186000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1866600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1734300</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,537 +4967,569 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>6000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>9700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>8700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>14800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>31100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>31800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>38800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>21900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>19700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>29800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>27100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>18600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>29400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>9700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>11700</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>757200</v>
+        <v>433900</v>
       </c>
       <c r="E58" s="3">
-        <v>806000</v>
+        <v>620400</v>
       </c>
       <c r="F58" s="3">
-        <v>1086600</v>
+        <v>752500</v>
       </c>
       <c r="G58" s="3">
-        <v>1058900</v>
+        <v>801000</v>
       </c>
       <c r="H58" s="3">
-        <v>1008800</v>
+        <v>1079800</v>
       </c>
       <c r="I58" s="3">
+        <v>1052300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1002500</v>
+      </c>
+      <c r="K58" s="3">
         <v>648600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>571500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>676700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>699600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>755800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>912700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>906600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1003500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1045300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1007500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>882800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>701900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>657800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>605900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>738400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>951600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1402200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1893600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1587100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1618800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1541700</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>994700</v>
+        <v>1087500</v>
       </c>
       <c r="E59" s="3">
-        <v>834500</v>
+        <v>1075500</v>
       </c>
       <c r="F59" s="3">
-        <v>748300</v>
+        <v>988500</v>
       </c>
       <c r="G59" s="3">
-        <v>672700</v>
+        <v>829400</v>
       </c>
       <c r="H59" s="3">
-        <v>670400</v>
+        <v>743600</v>
       </c>
       <c r="I59" s="3">
+        <v>668600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>666200</v>
+      </c>
+      <c r="K59" s="3">
         <v>665700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>696400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>727700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>721300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>719300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>680900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>760500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1045100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1055700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1077900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>595500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>535200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>442300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>415200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>406500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>321700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>293700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>242300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>292200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>186800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>158000</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1753900</v>
+        <v>1525900</v>
       </c>
       <c r="E60" s="3">
-        <v>1646000</v>
+        <v>1702800</v>
       </c>
       <c r="F60" s="3">
-        <v>1839900</v>
+        <v>1743100</v>
       </c>
       <c r="G60" s="3">
-        <v>1735200</v>
+        <v>1635900</v>
       </c>
       <c r="H60" s="3">
-        <v>1683800</v>
+        <v>1828500</v>
       </c>
       <c r="I60" s="3">
+        <v>1724500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>1673400</v>
+      </c>
+      <c r="K60" s="3">
         <v>1322600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1271400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1406600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1423600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1480400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1599700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1673100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2058300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2109800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2100300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1509400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1269000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1138900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1043000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1164600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1303200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1723000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2154400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1908700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1815300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1711400</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>166900</v>
+        <v>302900</v>
       </c>
       <c r="E61" s="3">
-        <v>357500</v>
+        <v>135400</v>
       </c>
       <c r="F61" s="3">
-        <v>306600</v>
+        <v>165800</v>
       </c>
       <c r="G61" s="3">
-        <v>206400</v>
+        <v>355300</v>
       </c>
       <c r="H61" s="3">
-        <v>301400</v>
+        <v>304700</v>
       </c>
       <c r="I61" s="3">
+        <v>205100</v>
+      </c>
+      <c r="J61" s="3">
+        <v>299600</v>
+      </c>
+      <c r="K61" s="3">
         <v>578700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>507700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>356200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>371700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>358500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>308400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>382200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>469300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>440800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>441600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>384400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>338000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>4000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>32100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>22900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>52200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>47300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>35300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>24800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>19900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>5000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>16600</v>
+        <v>15500</v>
       </c>
       <c r="E62" s="3">
-        <v>14700</v>
+        <v>17400</v>
       </c>
       <c r="F62" s="3">
-        <v>20000</v>
+        <v>16500</v>
       </c>
       <c r="G62" s="3">
-        <v>21600</v>
+        <v>14600</v>
       </c>
       <c r="H62" s="3">
-        <v>22300</v>
+        <v>19800</v>
       </c>
       <c r="I62" s="3">
+        <v>21500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>22200</v>
+      </c>
+      <c r="K62" s="3">
         <v>29500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>29300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>26500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>26000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>8200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>7400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>6800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>10300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>11700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>10000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>52000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>51700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>42600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>33400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>27200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5251,17 +5542,23 @@
       <c r="AC62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1937400</v>
+        <v>1844400</v>
       </c>
       <c r="E66" s="3">
-        <v>2018300</v>
+        <v>1855600</v>
       </c>
       <c r="F66" s="3">
-        <v>2166400</v>
+        <v>1925400</v>
       </c>
       <c r="G66" s="3">
-        <v>1963200</v>
+        <v>2005800</v>
       </c>
       <c r="H66" s="3">
-        <v>2013200</v>
+        <v>2153000</v>
       </c>
       <c r="I66" s="3">
+        <v>1951100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>2000800</v>
+      </c>
+      <c r="K66" s="3">
         <v>1936500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1817100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1794800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1827100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1852900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1921300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2067700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2537800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2562200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2551900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1945800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1658700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1185500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1108400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1214700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1355400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1770300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2189700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1933500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1835100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1716400</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5924,22 +6259,28 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>100100</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AE70" s="3">
         <v>97600</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>969100</v>
+        <v>973900</v>
       </c>
       <c r="E72" s="3">
-        <v>917500</v>
+        <v>946000</v>
       </c>
       <c r="F72" s="3">
-        <v>868100</v>
+        <v>963100</v>
       </c>
       <c r="G72" s="3">
-        <v>822600</v>
+        <v>911900</v>
       </c>
       <c r="H72" s="3">
-        <v>780700</v>
+        <v>862700</v>
       </c>
       <c r="I72" s="3">
+        <v>817500</v>
+      </c>
+      <c r="J72" s="3">
+        <v>775800</v>
+      </c>
+      <c r="K72" s="3">
         <v>742400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>719500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>703800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>688200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>605600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>499000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>384600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>332100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>281300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>235000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>629300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>549500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>443800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>361300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>260300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>74600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>30400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-35600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-58600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-72800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-82900</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1358500</v>
+        <v>1373100</v>
       </c>
       <c r="E76" s="3">
-        <v>1303100</v>
+        <v>1341500</v>
       </c>
       <c r="F76" s="3">
-        <v>1253100</v>
+        <v>1350100</v>
       </c>
       <c r="G76" s="3">
-        <v>1202300</v>
+        <v>1295100</v>
       </c>
       <c r="H76" s="3">
-        <v>1156200</v>
+        <v>1245300</v>
       </c>
       <c r="I76" s="3">
+        <v>1194900</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1149000</v>
+      </c>
+      <c r="K76" s="3">
         <v>1130800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1128400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1108500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1097000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1007800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>898000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>764300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>725000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>667500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>640500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1016200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>927400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>817700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>718000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>596400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>394200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>342900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>276500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>252500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-68600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-79700</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>51500</v>
+        <v>27900</v>
       </c>
       <c r="E81" s="3">
-        <v>49500</v>
+        <v>1700</v>
       </c>
       <c r="F81" s="3">
-        <v>45500</v>
+        <v>51200</v>
       </c>
       <c r="G81" s="3">
-        <v>41900</v>
+        <v>49100</v>
       </c>
       <c r="H81" s="3">
-        <v>38300</v>
+        <v>45200</v>
       </c>
       <c r="I81" s="3">
+        <v>41600</v>
+      </c>
+      <c r="J81" s="3">
+        <v>38100</v>
+      </c>
+      <c r="K81" s="3">
         <v>22900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>10900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>35300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>82500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>111800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>102200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>70900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>50800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>61700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-107000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>79700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>111500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>98000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>64500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>152400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>62600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>92900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>25500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>3200</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>800</v>
-      </c>
-      <c r="AC81" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD81" s="3">
         <v>800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6880,14 +7277,14 @@
         <v>0</v>
       </c>
       <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
         <v>800</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>10</v>
       </c>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7784,14 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7432,14 +7865,14 @@
         <v>0</v>
       </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>99300</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>10</v>
       </c>
@@ -7449,8 +7882,14 @@
       <c r="AF89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7558,14 +7999,14 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-800</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>10</v>
       </c>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +8212,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7834,14 +8293,14 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-187300</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>10</v>
       </c>
@@ -7851,8 +8310,14 @@
       <c r="AF94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8738,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8328,14 +8819,14 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>180500</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>10</v>
       </c>
@@ -8345,8 +8836,14 @@
       <c r="AF100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8420,14 +8917,14 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD101" s="3" t="s">
         <v>10</v>
       </c>
@@ -8437,8 +8934,14 @@
       <c r="AF101" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH101" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8512,14 +9015,14 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>92300</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>10</v>
       </c>
@@ -8527,6 +9030,12 @@
         <v>10</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>LX</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>447900</v>
+        <v>513300</v>
       </c>
       <c r="E8" s="3">
-        <v>484900</v>
+        <v>457000</v>
       </c>
       <c r="F8" s="3">
-        <v>484800</v>
+        <v>494800</v>
       </c>
       <c r="G8" s="3">
+        <v>494700</v>
+      </c>
+      <c r="H8" s="3">
+        <v>430800</v>
+      </c>
+      <c r="I8" s="3">
+        <v>420500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>430000</v>
+      </c>
+      <c r="K8" s="3">
+        <v>371700</v>
+      </c>
+      <c r="L8" s="3">
+        <v>335400</v>
+      </c>
+      <c r="M8" s="3">
+        <v>238100</v>
+      </c>
+      <c r="N8" s="3">
+        <v>303700</v>
+      </c>
+      <c r="O8" s="3">
+        <v>422000</v>
+      </c>
+      <c r="P8" s="3">
+        <v>464700</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>422800</v>
+      </c>
+      <c r="R8" s="3">
         <v>422200</v>
       </c>
-      <c r="H8" s="3">
-        <v>412100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>421400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>371700</v>
-      </c>
-      <c r="K8" s="3">
-        <v>335400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>238100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>303700</v>
-      </c>
-      <c r="N8" s="3">
-        <v>422000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>464700</v>
-      </c>
-      <c r="P8" s="3">
-        <v>422800</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>422200</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>464800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>435900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>394400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>484700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>490900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>388900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>269900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>370200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>258900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>285400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>231500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>236500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>215600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>195500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>177200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>202100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>282600</v>
+        <v>323200</v>
       </c>
       <c r="E9" s="3">
-        <v>311000</v>
+        <v>288300</v>
       </c>
       <c r="F9" s="3">
-        <v>297400</v>
+        <v>317400</v>
       </c>
       <c r="G9" s="3">
-        <v>284700</v>
+        <v>303500</v>
       </c>
       <c r="H9" s="3">
-        <v>287300</v>
+        <v>290500</v>
       </c>
       <c r="I9" s="3">
-        <v>277300</v>
+        <v>293200</v>
       </c>
       <c r="J9" s="3">
+        <v>282900</v>
+      </c>
+      <c r="K9" s="3">
         <v>247700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>247400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>174000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>136300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>207900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>228500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>226200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>210600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>320600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>293300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>368100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>257200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>229000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>217500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>160900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>173000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>151500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>164000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>166700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>182200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>165500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>154200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>137800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>167000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>125700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>165300</v>
+        <v>190100</v>
       </c>
       <c r="E10" s="3">
-        <v>173800</v>
+        <v>168700</v>
       </c>
       <c r="F10" s="3">
-        <v>187400</v>
+        <v>177400</v>
       </c>
       <c r="G10" s="3">
-        <v>137500</v>
+        <v>191200</v>
       </c>
       <c r="H10" s="3">
-        <v>124800</v>
+        <v>140300</v>
       </c>
       <c r="I10" s="3">
-        <v>144200</v>
+        <v>127300</v>
       </c>
       <c r="J10" s="3">
+        <v>147100</v>
+      </c>
+      <c r="K10" s="3">
         <v>124000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>88000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>64100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>167400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>214200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>236200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>196600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>211600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>144100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>142600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>227500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>261900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>171400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>109000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>197200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>107400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>121500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>64800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>54300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>50100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>41200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>39400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>35200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>19200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>17800</v>
+      </c>
+      <c r="H12" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I12" s="3">
+        <v>18300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>19100</v>
+      </c>
+      <c r="K12" s="3">
+        <v>19400</v>
+      </c>
+      <c r="L12" s="3">
+        <v>21500</v>
+      </c>
+      <c r="M12" s="3">
+        <v>21200</v>
+      </c>
+      <c r="N12" s="3">
+        <v>22600</v>
+      </c>
+      <c r="O12" s="3">
         <v>18600</v>
       </c>
-      <c r="E12" s="3">
-        <v>18800</v>
-      </c>
-      <c r="F12" s="3">
-        <v>17500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>16800</v>
-      </c>
-      <c r="H12" s="3">
-        <v>17900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>18700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>19400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>21500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>21200</v>
-      </c>
-      <c r="M12" s="3">
-        <v>22600</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
+        <v>18500</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>17800</v>
+      </c>
+      <c r="R12" s="3">
+        <v>13200</v>
+      </c>
+      <c r="S12" s="3">
+        <v>17400</v>
+      </c>
+      <c r="T12" s="3">
+        <v>19800</v>
+      </c>
+      <c r="U12" s="3">
+        <v>19900</v>
+      </c>
+      <c r="V12" s="3">
+        <v>15600</v>
+      </c>
+      <c r="W12" s="3">
         <v>18600</v>
       </c>
-      <c r="O12" s="3">
-        <v>18500</v>
-      </c>
-      <c r="P12" s="3">
-        <v>17800</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>13200</v>
-      </c>
-      <c r="R12" s="3">
-        <v>17400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>19800</v>
-      </c>
-      <c r="T12" s="3">
+      <c r="X12" s="3">
+        <v>15600</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>14300</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>13100</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AD12" s="3">
         <v>19900</v>
       </c>
-      <c r="U12" s="3">
-        <v>15600</v>
-      </c>
-      <c r="V12" s="3">
-        <v>18600</v>
-      </c>
-      <c r="W12" s="3">
-        <v>15600</v>
-      </c>
-      <c r="X12" s="3">
-        <v>14300</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>11600</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>13100</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>11000</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>9800</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>19900</v>
-      </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>8500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1347,38 +1367,38 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3">
         <v>4700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>5200</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1390,23 +1410,23 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>700</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3">
         <v>100</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1414,13 +1434,16 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>800</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>423500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>378900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>412400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>391300</v>
+      </c>
+      <c r="H17" s="3">
+        <v>385100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>387200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>375400</v>
+      </c>
+      <c r="K17" s="3">
+        <v>340200</v>
+      </c>
+      <c r="L17" s="3">
+        <v>351000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>261600</v>
+      </c>
+      <c r="N17" s="3">
+        <v>220400</v>
+      </c>
+      <c r="O17" s="3">
+        <v>310600</v>
+      </c>
+      <c r="P17" s="3">
+        <v>334500</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>312400</v>
+      </c>
+      <c r="R17" s="3">
+        <v>293800</v>
+      </c>
+      <c r="S17" s="3">
+        <v>411400</v>
+      </c>
+      <c r="T17" s="3">
+        <v>378100</v>
+      </c>
+      <c r="U17" s="3">
+        <v>443700</v>
+      </c>
+      <c r="V17" s="3">
         <v>371300</v>
       </c>
-      <c r="E17" s="3">
-        <v>404100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>383400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>377400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>379400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>367900</v>
-      </c>
-      <c r="J17" s="3">
-        <v>340200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>351000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>261600</v>
-      </c>
-      <c r="M17" s="3">
-        <v>220400</v>
-      </c>
-      <c r="N17" s="3">
-        <v>310600</v>
-      </c>
-      <c r="O17" s="3">
-        <v>334500</v>
-      </c>
-      <c r="P17" s="3">
-        <v>312400</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>293800</v>
-      </c>
-      <c r="R17" s="3">
-        <v>411400</v>
-      </c>
-      <c r="S17" s="3">
-        <v>378100</v>
-      </c>
-      <c r="T17" s="3">
-        <v>443700</v>
-      </c>
-      <c r="U17" s="3">
-        <v>371300</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>343000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>296900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>218100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>227900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>193700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>205600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>199500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>206600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>199300</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG17" s="3">
         <v>163100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>195600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>147300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>76600</v>
+        <v>89800</v>
       </c>
       <c r="E18" s="3">
-        <v>80700</v>
+        <v>78100</v>
       </c>
       <c r="F18" s="3">
-        <v>101300</v>
+        <v>82400</v>
       </c>
       <c r="G18" s="3">
-        <v>44800</v>
+        <v>103400</v>
       </c>
       <c r="H18" s="3">
-        <v>32700</v>
+        <v>45700</v>
       </c>
       <c r="I18" s="3">
-        <v>53600</v>
+        <v>33400</v>
       </c>
       <c r="J18" s="3">
+        <v>54700</v>
+      </c>
+      <c r="K18" s="3">
         <v>31500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>83200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>111500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>130100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>110300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>128400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>53400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>57800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-49300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>113400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>147900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>92000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>51800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>142200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>65200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>79800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>32000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>29900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>16300</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG18" s="3">
         <v>14100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,106 +1815,110 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-41300</v>
+        <v>-49400</v>
       </c>
       <c r="E20" s="3">
-        <v>-80400</v>
+        <v>-42200</v>
       </c>
       <c r="F20" s="3">
-        <v>-34200</v>
+        <v>-82000</v>
       </c>
       <c r="G20" s="3">
-        <v>15500</v>
+        <v>-34900</v>
       </c>
       <c r="H20" s="3">
-        <v>22800</v>
+        <v>15800</v>
       </c>
       <c r="I20" s="3">
-        <v>-1900</v>
+        <v>23300</v>
       </c>
       <c r="J20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K20" s="3">
         <v>16400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>44400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>37500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-41400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>10600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-44300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>15300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-77400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-18900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-17300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>22600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>26100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>41600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7600</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG20" s="3">
         <v>2100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1960,26 +1997,29 @@
       <c r="AB21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD21" s="3">
         <v>33000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH21" s="3">
         <v>6600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2025,8 +2065,8 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>10</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>10</v>
@@ -2043,237 +2083,246 @@
       <c r="W22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>35200</v>
+        <v>40400</v>
       </c>
       <c r="E23" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F23" s="3">
         <v>300</v>
       </c>
-      <c r="F23" s="3">
-        <v>67200</v>
-      </c>
       <c r="G23" s="3">
-        <v>60300</v>
+        <v>68500</v>
       </c>
       <c r="H23" s="3">
-        <v>55500</v>
+        <v>61500</v>
       </c>
       <c r="I23" s="3">
-        <v>51600</v>
+        <v>56600</v>
       </c>
       <c r="J23" s="3">
+        <v>52700</v>
+      </c>
+      <c r="K23" s="3">
         <v>47900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>28900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>97600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>133300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>121000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>84100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>57400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>73000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-126700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>94500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>130600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>114600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>77600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>183200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>73000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>78200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>31500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>31100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>13100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>7400</v>
+        <v>8500</v>
       </c>
       <c r="E24" s="3">
-        <v>-1300</v>
+        <v>7500</v>
       </c>
       <c r="F24" s="3">
-        <v>16000</v>
+        <v>-1400</v>
       </c>
       <c r="G24" s="3">
-        <v>11200</v>
+        <v>16300</v>
       </c>
       <c r="H24" s="3">
+        <v>11400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>10200</v>
+      </c>
+      <c r="K24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="L24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="M24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N24" s="3">
+        <v>6500</v>
+      </c>
+      <c r="O24" s="3">
+        <v>15100</v>
+      </c>
+      <c r="P24" s="3">
+        <v>21500</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>18900</v>
+      </c>
+      <c r="R24" s="3">
+        <v>13100</v>
+      </c>
+      <c r="S24" s="3">
+        <v>6600</v>
+      </c>
+      <c r="T24" s="3">
+        <v>11300</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="V24" s="3">
+        <v>14800</v>
+      </c>
+      <c r="W24" s="3">
+        <v>19100</v>
+      </c>
+      <c r="X24" s="3">
+        <v>16600</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>30700</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>10500</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>16200</v>
+      </c>
+      <c r="AE24" s="3">
         <v>10300</v>
       </c>
-      <c r="I24" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>9800</v>
-      </c>
-      <c r="K24" s="3">
-        <v>5600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>2700</v>
-      </c>
-      <c r="M24" s="3">
-        <v>6500</v>
-      </c>
-      <c r="N24" s="3">
-        <v>15100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>21500</v>
-      </c>
-      <c r="P24" s="3">
-        <v>18900</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>13100</v>
-      </c>
-      <c r="R24" s="3">
-        <v>6600</v>
-      </c>
-      <c r="S24" s="3">
-        <v>11300</v>
-      </c>
-      <c r="T24" s="3">
-        <v>-19700</v>
-      </c>
-      <c r="U24" s="3">
-        <v>14800</v>
-      </c>
-      <c r="V24" s="3">
-        <v>19100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>16600</v>
-      </c>
-      <c r="X24" s="3">
-        <v>13000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>30700</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>10500</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>-14700</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>5900</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>16200</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>10300</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4900</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>4700</v>
       </c>
       <c r="AH24" s="3">
         <v>4700</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>27900</v>
+        <v>31900</v>
       </c>
       <c r="E26" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F26" s="3">
         <v>1700</v>
       </c>
-      <c r="F26" s="3">
-        <v>51200</v>
-      </c>
       <c r="G26" s="3">
-        <v>49100</v>
+        <v>52300</v>
       </c>
       <c r="H26" s="3">
-        <v>45200</v>
+        <v>50200</v>
       </c>
       <c r="I26" s="3">
-        <v>41600</v>
+        <v>46200</v>
       </c>
       <c r="J26" s="3">
+        <v>42500</v>
+      </c>
+      <c r="K26" s="3">
         <v>38100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>23300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>35300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>82600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>111800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>102100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>70900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>50800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>61700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-107000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>79700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>111500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>98000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>64500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>152400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>62600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>92900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>25500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>14900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>10100</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG26" s="3">
         <v>8200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>27900</v>
+        <v>31900</v>
       </c>
       <c r="E27" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F27" s="3">
         <v>1700</v>
       </c>
-      <c r="F27" s="3">
-        <v>51200</v>
-      </c>
       <c r="G27" s="3">
-        <v>49100</v>
+        <v>52300</v>
       </c>
       <c r="H27" s="3">
-        <v>45200</v>
+        <v>50200</v>
       </c>
       <c r="I27" s="3">
-        <v>41600</v>
+        <v>46200</v>
       </c>
       <c r="J27" s="3">
+        <v>42500</v>
+      </c>
+      <c r="K27" s="3">
         <v>38100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>22900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>82500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>111800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>102200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>70900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>50800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>61700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-107000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>79700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>111500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>98000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>64500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>152400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>62600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>92900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>25500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>800</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG27" s="3">
         <v>800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>41300</v>
+        <v>49400</v>
       </c>
       <c r="E32" s="3">
-        <v>80400</v>
+        <v>42200</v>
       </c>
       <c r="F32" s="3">
-        <v>34200</v>
+        <v>82000</v>
       </c>
       <c r="G32" s="3">
-        <v>-15500</v>
+        <v>34900</v>
       </c>
       <c r="H32" s="3">
-        <v>-22800</v>
+        <v>-15800</v>
       </c>
       <c r="I32" s="3">
-        <v>1900</v>
+        <v>-23300</v>
       </c>
       <c r="J32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-16400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-44400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-37500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>41400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>44300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-15300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>77400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>18900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>17300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-22600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-26100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-41600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>27900</v>
+        <v>31900</v>
       </c>
       <c r="E33" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F33" s="3">
         <v>1700</v>
       </c>
-      <c r="F33" s="3">
-        <v>51200</v>
-      </c>
       <c r="G33" s="3">
-        <v>49100</v>
+        <v>52300</v>
       </c>
       <c r="H33" s="3">
-        <v>45200</v>
+        <v>50200</v>
       </c>
       <c r="I33" s="3">
-        <v>41600</v>
+        <v>46200</v>
       </c>
       <c r="J33" s="3">
+        <v>42500</v>
+      </c>
+      <c r="K33" s="3">
         <v>38100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>22900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>82500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>111800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>102200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>70900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>50800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>61700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-107000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>79700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>111500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>98000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>64500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>152400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>62600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>92900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>25500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>800</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG33" s="3">
         <v>800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>27900</v>
+        <v>31900</v>
       </c>
       <c r="E35" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F35" s="3">
         <v>1700</v>
       </c>
-      <c r="F35" s="3">
-        <v>51200</v>
-      </c>
       <c r="G35" s="3">
-        <v>49100</v>
+        <v>52300</v>
       </c>
       <c r="H35" s="3">
-        <v>45200</v>
+        <v>50200</v>
       </c>
       <c r="I35" s="3">
-        <v>41600</v>
+        <v>46200</v>
       </c>
       <c r="J35" s="3">
+        <v>42500</v>
+      </c>
+      <c r="K35" s="3">
         <v>38100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>22900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>82500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>111800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>102200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>70900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>50800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>61700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-107000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>79700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>111500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>98000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>64500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>152400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>62600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>92900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>25500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>800</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG35" s="3">
         <v>800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,117 +3611,121 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>267700</v>
+        <v>295200</v>
       </c>
       <c r="E41" s="3">
-        <v>362600</v>
+        <v>273200</v>
       </c>
       <c r="F41" s="3">
-        <v>349100</v>
+        <v>370000</v>
       </c>
       <c r="G41" s="3">
-        <v>363000</v>
+        <v>356300</v>
       </c>
       <c r="H41" s="3">
-        <v>316700</v>
+        <v>370400</v>
       </c>
       <c r="I41" s="3">
-        <v>206400</v>
+        <v>323100</v>
       </c>
       <c r="J41" s="3">
+        <v>210600</v>
+      </c>
+      <c r="K41" s="3">
         <v>291300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>286500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>320200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>367900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>361900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>338900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>335900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>217700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>234800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>171600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>204100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>321100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>431100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>165300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>204100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>166800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>61700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>61600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>88000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>167200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>74900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>145700</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="3">
-        <v>27600</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>10</v>
+      <c r="E42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3">
+        <v>28200</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -3643,11 +3733,11 @@
       <c r="H42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I42" s="3">
-        <v>37300</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>10</v>
+      <c r="I42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J42" s="3">
+        <v>38100</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>10</v>
@@ -3664,8 +3754,8 @@
       <c r="O42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -3721,653 +3811,674 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1479300</v>
+        <v>1475800</v>
       </c>
       <c r="E43" s="3">
-        <v>1390400</v>
+        <v>1509500</v>
       </c>
       <c r="F43" s="3">
-        <v>1358700</v>
+        <v>1418800</v>
       </c>
       <c r="G43" s="3">
-        <v>1344100</v>
+        <v>1386400</v>
       </c>
       <c r="H43" s="3">
-        <v>1348700</v>
+        <v>1371500</v>
       </c>
       <c r="I43" s="3">
-        <v>1422900</v>
+        <v>1376200</v>
       </c>
       <c r="J43" s="3">
+        <v>1451900</v>
+      </c>
+      <c r="K43" s="3">
         <v>1406500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1299400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1166100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1183700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1143300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1213000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1206900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1370400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1473600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1384300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1357000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1226000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1001000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>900300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>875300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>953400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>957000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1390300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1719200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1509000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1421400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1287700</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4100</v>
+        <v>6300</v>
       </c>
       <c r="E44" s="3">
-        <v>4600</v>
+        <v>4200</v>
       </c>
       <c r="F44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G44" s="3">
+        <v>8100</v>
+      </c>
+      <c r="H44" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I44" s="3">
+        <v>7200</v>
+      </c>
+      <c r="J44" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K44" s="3">
+        <v>12000</v>
+      </c>
+      <c r="L44" s="3">
+        <v>9400</v>
+      </c>
+      <c r="M44" s="3">
         <v>7900</v>
       </c>
-      <c r="G44" s="3">
-        <v>7600</v>
-      </c>
-      <c r="H44" s="3">
-        <v>7000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>7400</v>
-      </c>
-      <c r="J44" s="3">
-        <v>12000</v>
-      </c>
-      <c r="K44" s="3">
-        <v>9400</v>
-      </c>
-      <c r="L44" s="3">
-        <v>7900</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>16400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>21400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>15800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>8300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>13300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>10600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>13600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>15100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>18500</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG44" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH44" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>881000</v>
+        <v>863200</v>
       </c>
       <c r="E45" s="3">
-        <v>771000</v>
+        <v>899000</v>
       </c>
       <c r="F45" s="3">
-        <v>851200</v>
+        <v>786800</v>
       </c>
       <c r="G45" s="3">
-        <v>859500</v>
+        <v>868500</v>
       </c>
       <c r="H45" s="3">
-        <v>1020600</v>
+        <v>877100</v>
       </c>
       <c r="I45" s="3">
-        <v>782700</v>
+        <v>1041500</v>
       </c>
       <c r="J45" s="3">
+        <v>798700</v>
+      </c>
+      <c r="K45" s="3">
         <v>747300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>784900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>822800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>741600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>802100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>718700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>709200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>690800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1001300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1110800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1018200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>978100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>710400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>581500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>421600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>368100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>409800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>286300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>266700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>199200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>111500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>70400</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2632100</v>
+        <v>2640500</v>
       </c>
       <c r="E46" s="3">
-        <v>2556400</v>
+        <v>2685900</v>
       </c>
       <c r="F46" s="3">
-        <v>2566900</v>
+        <v>2608600</v>
       </c>
       <c r="G46" s="3">
-        <v>2574200</v>
+        <v>2619300</v>
       </c>
       <c r="H46" s="3">
-        <v>2693000</v>
+        <v>2626800</v>
       </c>
       <c r="I46" s="3">
-        <v>2456800</v>
+        <v>2748000</v>
       </c>
       <c r="J46" s="3">
+        <v>2506900</v>
+      </c>
+      <c r="K46" s="3">
         <v>2457100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2380100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2317100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2299800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2314800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2277100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2261600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2285400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2718400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2675000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2588000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2541600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2163900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1662800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1509400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1496600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1441900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1748800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2087400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1890500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1626700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1522300</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>113200</v>
+        <v>112600</v>
       </c>
       <c r="E47" s="3">
-        <v>145800</v>
+        <v>115500</v>
       </c>
       <c r="F47" s="3">
-        <v>184100</v>
+        <v>148800</v>
       </c>
       <c r="G47" s="3">
-        <v>204800</v>
+        <v>187800</v>
       </c>
       <c r="H47" s="3">
-        <v>196800</v>
+        <v>209000</v>
       </c>
       <c r="I47" s="3">
-        <v>195300</v>
+        <v>200800</v>
       </c>
       <c r="J47" s="3">
+        <v>199300</v>
+      </c>
+      <c r="K47" s="3">
         <v>195600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>185900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>144900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>145900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>168900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>183700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>194400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>198700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>197200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>212500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>249100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>297900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>310000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>258300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>248900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>272600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>253800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>314900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>349900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>268400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>218800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>194900</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>66900</v>
+        <v>77300</v>
       </c>
       <c r="E48" s="3">
-        <v>61700</v>
+        <v>68200</v>
       </c>
       <c r="F48" s="3">
-        <v>59100</v>
+        <v>63000</v>
       </c>
       <c r="G48" s="3">
-        <v>53300</v>
+        <v>60300</v>
       </c>
       <c r="H48" s="3">
-        <v>45200</v>
+        <v>54300</v>
       </c>
       <c r="I48" s="3">
-        <v>39300</v>
+        <v>46100</v>
       </c>
       <c r="J48" s="3">
+        <v>40100</v>
+      </c>
+      <c r="K48" s="3">
         <v>33500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8700</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>122800</v>
+        <v>124100</v>
       </c>
       <c r="E49" s="3">
-        <v>124000</v>
+        <v>125300</v>
       </c>
       <c r="F49" s="3">
-        <v>125200</v>
+        <v>126500</v>
       </c>
       <c r="G49" s="3">
-        <v>126300</v>
+        <v>127700</v>
       </c>
       <c r="H49" s="3">
-        <v>127500</v>
+        <v>128900</v>
       </c>
       <c r="I49" s="3">
-        <v>128700</v>
+        <v>130100</v>
       </c>
       <c r="J49" s="3">
+        <v>131300</v>
+      </c>
+      <c r="K49" s="3">
         <v>129900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>131900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>133100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>133400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>138500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>139800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>142500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>139300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>148700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>150000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>161900</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>10</v>
       </c>
@@ -4380,8 +4491,8 @@
       <c r="Y49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>282500</v>
+        <v>290800</v>
       </c>
       <c r="E52" s="3">
-        <v>309300</v>
+        <v>288300</v>
       </c>
       <c r="F52" s="3">
-        <v>340200</v>
+        <v>315600</v>
       </c>
       <c r="G52" s="3">
-        <v>342200</v>
+        <v>347200</v>
       </c>
       <c r="H52" s="3">
-        <v>335900</v>
+        <v>349100</v>
       </c>
       <c r="I52" s="3">
-        <v>325900</v>
+        <v>342700</v>
       </c>
       <c r="J52" s="3">
+        <v>332500</v>
+      </c>
+      <c r="K52" s="3">
         <v>333600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>339300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>320600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>297300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>279600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>241400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>202900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>191200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>183300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>176700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>177400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>108200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>98300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>67800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>54000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>29900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>42900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>38800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>18600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8400</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3217500</v>
+        <v>3245300</v>
       </c>
       <c r="E54" s="3">
-        <v>3197100</v>
+        <v>3283100</v>
       </c>
       <c r="F54" s="3">
-        <v>3275500</v>
+        <v>3262400</v>
       </c>
       <c r="G54" s="3">
-        <v>3300800</v>
+        <v>3342300</v>
       </c>
       <c r="H54" s="3">
-        <v>3398400</v>
+        <v>3368200</v>
       </c>
       <c r="I54" s="3">
-        <v>3146000</v>
+        <v>3467700</v>
       </c>
       <c r="J54" s="3">
+        <v>3210200</v>
+      </c>
+      <c r="K54" s="3">
         <v>3149800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3067300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2945600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2903300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2924100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2860800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2819200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2832000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3262900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3229800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3192300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2962000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2586100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2003200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1826400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1811100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1749600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2113200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2466200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2186000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1866600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1734300</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,570 +5099,586 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
-        <v>6900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>4600</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>31100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>31800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>38800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>21900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>19700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>29800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>27100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>18600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>29400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11700</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>433900</v>
+        <v>416400</v>
       </c>
       <c r="E58" s="3">
-        <v>620400</v>
+        <v>442700</v>
       </c>
       <c r="F58" s="3">
-        <v>752500</v>
+        <v>633100</v>
       </c>
       <c r="G58" s="3">
-        <v>801000</v>
+        <v>767900</v>
       </c>
       <c r="H58" s="3">
-        <v>1079800</v>
+        <v>817300</v>
       </c>
       <c r="I58" s="3">
-        <v>1052300</v>
+        <v>1101900</v>
       </c>
       <c r="J58" s="3">
+        <v>1073800</v>
+      </c>
+      <c r="K58" s="3">
         <v>1002500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>648600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>571500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>676700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>699600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>755800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>912700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>906600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1003500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1045300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1007500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>882800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>701900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>657800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>605900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>738400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>951600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1402200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1893600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1587100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1618800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1541700</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1087500</v>
+        <v>1065800</v>
       </c>
       <c r="E59" s="3">
-        <v>1075500</v>
+        <v>1109700</v>
       </c>
       <c r="F59" s="3">
-        <v>988500</v>
+        <v>1097400</v>
       </c>
       <c r="G59" s="3">
-        <v>829400</v>
+        <v>1008700</v>
       </c>
       <c r="H59" s="3">
-        <v>743600</v>
+        <v>846300</v>
       </c>
       <c r="I59" s="3">
-        <v>668600</v>
+        <v>758800</v>
       </c>
       <c r="J59" s="3">
+        <v>682200</v>
+      </c>
+      <c r="K59" s="3">
         <v>666200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>665700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>696400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>727700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>721300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>719300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>680900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>760500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1045100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1055700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1077900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>595500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>535200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>442300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>415200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>406500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>321700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>293700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>242300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>292200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>186800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>158000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1525900</v>
+        <v>1488300</v>
       </c>
       <c r="E60" s="3">
-        <v>1702800</v>
+        <v>1557100</v>
       </c>
       <c r="F60" s="3">
-        <v>1743100</v>
+        <v>1737500</v>
       </c>
       <c r="G60" s="3">
-        <v>1635900</v>
+        <v>1778700</v>
       </c>
       <c r="H60" s="3">
-        <v>1828500</v>
+        <v>1669300</v>
       </c>
       <c r="I60" s="3">
-        <v>1724500</v>
+        <v>1865900</v>
       </c>
       <c r="J60" s="3">
+        <v>1759700</v>
+      </c>
+      <c r="K60" s="3">
         <v>1673400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1322600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1271400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1406600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1423600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1480400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1599700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1673100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2058300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2109800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2100300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1509400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1269000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1138900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1043000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1164600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1303200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1723000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2154400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1908700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1815300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1711400</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>302900</v>
+        <v>317700</v>
       </c>
       <c r="E61" s="3">
-        <v>135400</v>
+        <v>309100</v>
       </c>
       <c r="F61" s="3">
-        <v>165800</v>
+        <v>138200</v>
       </c>
       <c r="G61" s="3">
-        <v>355300</v>
+        <v>169200</v>
       </c>
       <c r="H61" s="3">
-        <v>304700</v>
+        <v>362600</v>
       </c>
       <c r="I61" s="3">
-        <v>205100</v>
+        <v>310900</v>
       </c>
       <c r="J61" s="3">
+        <v>209300</v>
+      </c>
+      <c r="K61" s="3">
         <v>299600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>578700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>507700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>356200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>371700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>358500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>308400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>382200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>469300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>440800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>441600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>384400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>338000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>32100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>22900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>52200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>47300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>24800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>19900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5000</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>15500</v>
+        <v>16700</v>
       </c>
       <c r="E62" s="3">
-        <v>17400</v>
+        <v>15800</v>
       </c>
       <c r="F62" s="3">
-        <v>16500</v>
+        <v>17800</v>
       </c>
       <c r="G62" s="3">
-        <v>14600</v>
+        <v>16800</v>
       </c>
       <c r="H62" s="3">
-        <v>19800</v>
+        <v>14900</v>
       </c>
       <c r="I62" s="3">
-        <v>21500</v>
+        <v>20200</v>
       </c>
       <c r="J62" s="3">
+        <v>21900</v>
+      </c>
+      <c r="K62" s="3">
         <v>22200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>52000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>51700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>42600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>33400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>27200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5548,8 +5694,8 @@
       <c r="AE62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AF62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1844400</v>
+        <v>1822700</v>
       </c>
       <c r="E66" s="3">
-        <v>1855600</v>
+        <v>1882000</v>
       </c>
       <c r="F66" s="3">
-        <v>1925400</v>
+        <v>1893500</v>
       </c>
       <c r="G66" s="3">
-        <v>2005800</v>
+        <v>1964700</v>
       </c>
       <c r="H66" s="3">
-        <v>2153000</v>
+        <v>2046700</v>
       </c>
       <c r="I66" s="3">
-        <v>1951100</v>
+        <v>2197000</v>
       </c>
       <c r="J66" s="3">
+        <v>1990900</v>
+      </c>
+      <c r="K66" s="3">
         <v>2000800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1936500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1817100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1794800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1827100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1852900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1921300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2067700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2537800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2562200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2551900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1945800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1658700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1185500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1108400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1214700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1355400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1770300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2189700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1933500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1835100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1716400</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6265,22 +6433,25 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>100100</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>97600</v>
       </c>
-      <c r="AF70" s="3">
-        <v>0</v>
-      </c>
       <c r="AG70" s="3">
         <v>0</v>
       </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>973900</v>
+        <v>1013600</v>
       </c>
       <c r="E72" s="3">
-        <v>946000</v>
+        <v>993700</v>
       </c>
       <c r="F72" s="3">
-        <v>963100</v>
+        <v>965300</v>
       </c>
       <c r="G72" s="3">
-        <v>911900</v>
+        <v>982700</v>
       </c>
       <c r="H72" s="3">
-        <v>862700</v>
+        <v>930500</v>
       </c>
       <c r="I72" s="3">
-        <v>817500</v>
+        <v>880300</v>
       </c>
       <c r="J72" s="3">
+        <v>834200</v>
+      </c>
+      <c r="K72" s="3">
         <v>775800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>742400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>719500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>703800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>688200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>605600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>499000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>384600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>332100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>281300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>235000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>629300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>549500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>443800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>361300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>260300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>74600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>30400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-35600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-58600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-72800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-82900</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1373100</v>
+        <v>1422600</v>
       </c>
       <c r="E76" s="3">
-        <v>1341500</v>
+        <v>1401100</v>
       </c>
       <c r="F76" s="3">
-        <v>1350100</v>
+        <v>1368900</v>
       </c>
       <c r="G76" s="3">
-        <v>1295100</v>
+        <v>1377600</v>
       </c>
       <c r="H76" s="3">
-        <v>1245300</v>
+        <v>1321500</v>
       </c>
       <c r="I76" s="3">
-        <v>1194900</v>
+        <v>1270800</v>
       </c>
       <c r="J76" s="3">
+        <v>1219300</v>
+      </c>
+      <c r="K76" s="3">
         <v>1149000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1130800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1128400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1108500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1097000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1007800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>898000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>764300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>725000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>667500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>640500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1016200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>927400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>817700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>718000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>596400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>394200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>342900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>276500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>252500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-68600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-79700</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>27900</v>
+        <v>31900</v>
       </c>
       <c r="E81" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F81" s="3">
         <v>1700</v>
       </c>
-      <c r="F81" s="3">
-        <v>51200</v>
-      </c>
       <c r="G81" s="3">
-        <v>49100</v>
+        <v>52300</v>
       </c>
       <c r="H81" s="3">
-        <v>45200</v>
+        <v>50200</v>
       </c>
       <c r="I81" s="3">
-        <v>41600</v>
+        <v>46200</v>
       </c>
       <c r="J81" s="3">
+        <v>42500</v>
+      </c>
+      <c r="K81" s="3">
         <v>38100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>22900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>82500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>111800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>102200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>70900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>50800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>61700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-107000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>79700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>111500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>98000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>64500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>152400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>62600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>92900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>25500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>800</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG81" s="3">
         <v>800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7283,11 +7482,11 @@
         <v>0</v>
       </c>
       <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
         <v>800</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>10</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,8 +8004,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7871,11 +8088,11 @@
         <v>0</v>
       </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>99300</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>10</v>
       </c>
@@ -7888,8 +8105,11 @@
       <c r="AH89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8005,11 +8226,11 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-800</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>10</v>
       </c>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8299,11 +8529,11 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-187300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>10</v>
       </c>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8825,11 +9071,11 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>180500</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>10</v>
       </c>
@@ -8842,8 +9088,11 @@
       <c r="AH100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8923,11 +9172,11 @@
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE101" s="3" t="s">
         <v>10</v>
       </c>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9021,11 +9273,11 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>92300</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>10</v>
       </c>
@@ -9036,6 +9288,9 @@
         <v>10</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>LX</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>513300</v>
+        <v>522100</v>
       </c>
       <c r="E8" s="3">
-        <v>457000</v>
+        <v>501000</v>
       </c>
       <c r="F8" s="3">
-        <v>494800</v>
+        <v>449000</v>
       </c>
       <c r="G8" s="3">
-        <v>494700</v>
+        <v>494900</v>
       </c>
       <c r="H8" s="3">
-        <v>430800</v>
+        <v>480900</v>
       </c>
       <c r="I8" s="3">
-        <v>420500</v>
+        <v>421400</v>
       </c>
       <c r="J8" s="3">
+        <v>434200</v>
+      </c>
+      <c r="K8" s="3">
         <v>430000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>371700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>335400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>238100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>303700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>422000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>464700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>422800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>422200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>464800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>435900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>394400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>484700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>490900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>388900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>269900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>370200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>258900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>285400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>231500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>236500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>215600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>195500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>177200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>202100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>323200</v>
+        <v>81100</v>
       </c>
       <c r="E9" s="3">
-        <v>288300</v>
+        <v>81700</v>
       </c>
       <c r="F9" s="3">
-        <v>317400</v>
+        <v>51600</v>
       </c>
       <c r="G9" s="3">
-        <v>303500</v>
+        <v>74000</v>
       </c>
       <c r="H9" s="3">
-        <v>290500</v>
+        <v>71500</v>
       </c>
       <c r="I9" s="3">
-        <v>293200</v>
+        <v>84300</v>
       </c>
       <c r="J9" s="3">
+        <v>88100</v>
+      </c>
+      <c r="K9" s="3">
         <v>282900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>247700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>247400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>174000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>136300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>207900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>228500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>226200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>210600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>320600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>293300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>368100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>257200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>229000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>217500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>160900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>173000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>151500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>164000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>166700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>182200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>165500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>154200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>137800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>167000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>125700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>190100</v>
+        <v>206900</v>
       </c>
       <c r="E10" s="3">
-        <v>168700</v>
+        <v>206800</v>
       </c>
       <c r="F10" s="3">
-        <v>177400</v>
+        <v>188700</v>
       </c>
       <c r="G10" s="3">
-        <v>191200</v>
+        <v>206000</v>
       </c>
       <c r="H10" s="3">
-        <v>140300</v>
+        <v>207700</v>
       </c>
       <c r="I10" s="3">
-        <v>127300</v>
+        <v>154500</v>
       </c>
       <c r="J10" s="3">
+        <v>152200</v>
+      </c>
+      <c r="K10" s="3">
         <v>147100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>124000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>64100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>167400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>214200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>236200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>196600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>211600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>144100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>142600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>227500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>261900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>171400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>109000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>197200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>107400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>121500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>64800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>54300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>50100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>41200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>39400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>35200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>20200</v>
+        <v>21200</v>
       </c>
       <c r="E12" s="3">
-        <v>19000</v>
+        <v>19700</v>
       </c>
       <c r="F12" s="3">
+        <v>18700</v>
+      </c>
+      <c r="G12" s="3">
         <v>19200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>17300</v>
+      </c>
+      <c r="I12" s="3">
+        <v>16700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>18900</v>
+      </c>
+      <c r="K12" s="3">
+        <v>19100</v>
+      </c>
+      <c r="L12" s="3">
+        <v>19400</v>
+      </c>
+      <c r="M12" s="3">
+        <v>21500</v>
+      </c>
+      <c r="N12" s="3">
+        <v>21200</v>
+      </c>
+      <c r="O12" s="3">
+        <v>22600</v>
+      </c>
+      <c r="P12" s="3">
+        <v>18600</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>18500</v>
+      </c>
+      <c r="R12" s="3">
         <v>17800</v>
       </c>
-      <c r="H12" s="3">
-        <v>17100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>18300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>19100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>19400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>21500</v>
-      </c>
-      <c r="M12" s="3">
-        <v>21200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>22600</v>
-      </c>
-      <c r="O12" s="3">
+      <c r="S12" s="3">
+        <v>13200</v>
+      </c>
+      <c r="T12" s="3">
+        <v>17400</v>
+      </c>
+      <c r="U12" s="3">
+        <v>19800</v>
+      </c>
+      <c r="V12" s="3">
+        <v>19900</v>
+      </c>
+      <c r="W12" s="3">
+        <v>15600</v>
+      </c>
+      <c r="X12" s="3">
         <v>18600</v>
       </c>
-      <c r="P12" s="3">
-        <v>18500</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>17800</v>
-      </c>
-      <c r="R12" s="3">
-        <v>13200</v>
-      </c>
-      <c r="S12" s="3">
-        <v>17400</v>
-      </c>
-      <c r="T12" s="3">
-        <v>19800</v>
-      </c>
-      <c r="U12" s="3">
+      <c r="Y12" s="3">
+        <v>15600</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>14300</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>13100</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AE12" s="3">
         <v>19900</v>
       </c>
-      <c r="V12" s="3">
-        <v>15600</v>
-      </c>
-      <c r="W12" s="3">
-        <v>18600</v>
-      </c>
-      <c r="X12" s="3">
-        <v>15600</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>14300</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>11600</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>13100</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>11000</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>9800</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>19900</v>
-      </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>10000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,67 +1358,70 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>42600</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="3">
         <v>4700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5200</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1413,23 +1433,23 @@
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1500</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>700</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="3">
         <v>100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
@@ -1437,36 +1457,39 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>800</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>423500</v>
+        <v>446300</v>
       </c>
       <c r="E17" s="3">
-        <v>378900</v>
+        <v>413300</v>
       </c>
       <c r="F17" s="3">
-        <v>412400</v>
+        <v>372200</v>
       </c>
       <c r="G17" s="3">
-        <v>391300</v>
+        <v>412500</v>
       </c>
       <c r="H17" s="3">
-        <v>385100</v>
+        <v>380400</v>
       </c>
       <c r="I17" s="3">
-        <v>387200</v>
+        <v>376600</v>
       </c>
       <c r="J17" s="3">
+        <v>399800</v>
+      </c>
+      <c r="K17" s="3">
         <v>375400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>340200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>351000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>261600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>220400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>310600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>334500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>312400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>293800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>411400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>378100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>443700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>371300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>343000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>296900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>218100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>227900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>193700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>205600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>199500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>206600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>199300</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH17" s="3">
         <v>163100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>195600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>147300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>89800</v>
+        <v>75800</v>
       </c>
       <c r="E18" s="3">
-        <v>78100</v>
+        <v>87700</v>
       </c>
       <c r="F18" s="3">
+        <v>76800</v>
+      </c>
+      <c r="G18" s="3">
         <v>82400</v>
       </c>
-      <c r="G18" s="3">
-        <v>103400</v>
-      </c>
       <c r="H18" s="3">
-        <v>45700</v>
+        <v>100500</v>
       </c>
       <c r="I18" s="3">
-        <v>33400</v>
+        <v>44700</v>
       </c>
       <c r="J18" s="3">
+        <v>34500</v>
+      </c>
+      <c r="K18" s="3">
         <v>54700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>31500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>83200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>111500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>130100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>110300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>128400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>53400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>57800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-49300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>113400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>147900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>92000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>51800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>142200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>65200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>79800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>32000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>29900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16300</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH18" s="3">
         <v>14100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,132 +1849,136 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-49400</v>
+        <v>20400</v>
       </c>
       <c r="E20" s="3">
-        <v>-42200</v>
+        <v>48500</v>
       </c>
       <c r="F20" s="3">
-        <v>-82000</v>
+        <v>40900</v>
       </c>
       <c r="G20" s="3">
-        <v>-34900</v>
+        <v>38000</v>
       </c>
       <c r="H20" s="3">
-        <v>15800</v>
+        <v>31900</v>
       </c>
       <c r="I20" s="3">
-        <v>23300</v>
+        <v>-18600</v>
       </c>
       <c r="J20" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>16400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>44400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>37500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-41400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-44300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>15300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-77400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-18900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-17300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>22600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>26100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>41600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7600</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH20" s="3">
         <v>2100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>10</v>
+      <c r="D21" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>42800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>39500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>48100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>71900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>66600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>62500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>10</v>
@@ -2000,49 +2037,52 @@
       <c r="AC21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE21" s="3">
         <v>33000</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI21" s="3">
         <v>6600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2068,8 +2108,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>10</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>10</v>
@@ -2086,243 +2126,252 @@
       <c r="X22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>40400</v>
+        <v>54400</v>
       </c>
       <c r="E23" s="3">
-        <v>36000</v>
+        <v>39400</v>
       </c>
       <c r="F23" s="3">
+        <v>35300</v>
+      </c>
+      <c r="G23" s="3">
         <v>300</v>
       </c>
-      <c r="G23" s="3">
-        <v>68500</v>
-      </c>
       <c r="H23" s="3">
-        <v>61500</v>
+        <v>66600</v>
       </c>
       <c r="I23" s="3">
-        <v>56600</v>
+        <v>60200</v>
       </c>
       <c r="J23" s="3">
+        <v>58500</v>
+      </c>
+      <c r="K23" s="3">
         <v>52700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>47900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>28900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>97600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>133300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>121000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>84100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>57400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>73000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-126700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>94500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>130600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>114600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>77600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>183200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>73000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>78200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>31500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>31100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>20400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>13100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>8500</v>
+        <v>10300</v>
       </c>
       <c r="E24" s="3">
-        <v>7500</v>
+        <v>8300</v>
       </c>
       <c r="F24" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G24" s="3">
         <v>-1400</v>
       </c>
-      <c r="G24" s="3">
-        <v>16300</v>
-      </c>
       <c r="H24" s="3">
-        <v>11400</v>
+        <v>15800</v>
       </c>
       <c r="I24" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K24" s="3">
+        <v>10200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="M24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O24" s="3">
+        <v>6500</v>
+      </c>
+      <c r="P24" s="3">
+        <v>15100</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>21500</v>
+      </c>
+      <c r="R24" s="3">
+        <v>18900</v>
+      </c>
+      <c r="S24" s="3">
+        <v>13100</v>
+      </c>
+      <c r="T24" s="3">
+        <v>6600</v>
+      </c>
+      <c r="U24" s="3">
+        <v>11300</v>
+      </c>
+      <c r="V24" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="W24" s="3">
+        <v>14800</v>
+      </c>
+      <c r="X24" s="3">
+        <v>19100</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>16600</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>30700</v>
+      </c>
+      <c r="AB24" s="3">
         <v>10500</v>
       </c>
-      <c r="J24" s="3">
-        <v>10200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>9800</v>
-      </c>
-      <c r="L24" s="3">
-        <v>5600</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2700</v>
-      </c>
-      <c r="N24" s="3">
-        <v>6500</v>
-      </c>
-      <c r="O24" s="3">
-        <v>15100</v>
-      </c>
-      <c r="P24" s="3">
-        <v>21500</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>18900</v>
-      </c>
-      <c r="R24" s="3">
-        <v>13100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>6600</v>
-      </c>
-      <c r="T24" s="3">
-        <v>11300</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-19700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>14800</v>
-      </c>
-      <c r="W24" s="3">
-        <v>19100</v>
-      </c>
-      <c r="X24" s="3">
-        <v>16600</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>13000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>30700</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>10500</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>16200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>10300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4900</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>4700</v>
       </c>
       <c r="AI24" s="3">
         <v>4700</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>4700</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>31900</v>
+        <v>44100</v>
       </c>
       <c r="E26" s="3">
-        <v>28400</v>
+        <v>31200</v>
       </c>
       <c r="F26" s="3">
+        <v>27900</v>
+      </c>
+      <c r="G26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
-        <v>52300</v>
-      </c>
       <c r="H26" s="3">
-        <v>50200</v>
+        <v>50800</v>
       </c>
       <c r="I26" s="3">
-        <v>46200</v>
+        <v>49100</v>
       </c>
       <c r="J26" s="3">
+        <v>47700</v>
+      </c>
+      <c r="K26" s="3">
         <v>42500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>38100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>35300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>82600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>111800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>102100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>70900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>50800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>61700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-107000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>79700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>111500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>98000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>64500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>152400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>62600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>92900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>25500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>14900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>10100</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH26" s="3">
         <v>8200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>31900</v>
+        <v>44100</v>
       </c>
       <c r="E27" s="3">
-        <v>28400</v>
+        <v>31200</v>
       </c>
       <c r="F27" s="3">
+        <v>27900</v>
+      </c>
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
-        <v>52300</v>
-      </c>
       <c r="H27" s="3">
-        <v>50200</v>
+        <v>50800</v>
       </c>
       <c r="I27" s="3">
-        <v>46200</v>
+        <v>49100</v>
       </c>
       <c r="J27" s="3">
+        <v>47700</v>
+      </c>
+      <c r="K27" s="3">
         <v>42500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>38100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>22900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>35300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>82500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>111800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>102200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>70900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>50800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>61700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-107000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>79700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>111500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>98000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>64500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>152400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>62600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>92900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>25500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>800</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH27" s="3">
         <v>800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>49400</v>
+        <v>-20400</v>
       </c>
       <c r="E32" s="3">
-        <v>42200</v>
+        <v>-48500</v>
       </c>
       <c r="F32" s="3">
-        <v>82000</v>
+        <v>-40900</v>
       </c>
       <c r="G32" s="3">
-        <v>34900</v>
+        <v>-38000</v>
       </c>
       <c r="H32" s="3">
-        <v>-15800</v>
+        <v>-31900</v>
       </c>
       <c r="I32" s="3">
-        <v>-23300</v>
+        <v>18600</v>
       </c>
       <c r="J32" s="3">
+        <v>24600</v>
+      </c>
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-16400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-44400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-37500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>41400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>44300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-15300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>77400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>18900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>17300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-22600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-41600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>31900</v>
+        <v>44100</v>
       </c>
       <c r="E33" s="3">
-        <v>28400</v>
+        <v>31200</v>
       </c>
       <c r="F33" s="3">
+        <v>27900</v>
+      </c>
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
-        <v>52300</v>
-      </c>
       <c r="H33" s="3">
-        <v>50200</v>
+        <v>50800</v>
       </c>
       <c r="I33" s="3">
-        <v>46200</v>
+        <v>49100</v>
       </c>
       <c r="J33" s="3">
+        <v>47700</v>
+      </c>
+      <c r="K33" s="3">
         <v>42500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>38100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>22900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>35300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>82500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>111800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>102200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>70900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>50800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>61700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-107000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>79700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>111500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>98000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>64500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>152400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>62600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>92900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>25500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>800</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH33" s="3">
         <v>800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>31900</v>
+        <v>44100</v>
       </c>
       <c r="E35" s="3">
-        <v>28400</v>
+        <v>31200</v>
       </c>
       <c r="F35" s="3">
+        <v>27900</v>
+      </c>
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
-        <v>52300</v>
-      </c>
       <c r="H35" s="3">
-        <v>50200</v>
+        <v>50800</v>
       </c>
       <c r="I35" s="3">
-        <v>46200</v>
+        <v>49100</v>
       </c>
       <c r="J35" s="3">
+        <v>47700</v>
+      </c>
+      <c r="K35" s="3">
         <v>42500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>38100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>22900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>35300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>82500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>111800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>102200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>70900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>50800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>61700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-107000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>79700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>111500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>98000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>64500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>152400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>62600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>92900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>25500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>800</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH35" s="3">
         <v>800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,136 +3698,140 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>295200</v>
+        <v>307000</v>
       </c>
       <c r="E41" s="3">
-        <v>273200</v>
+        <v>288100</v>
       </c>
       <c r="F41" s="3">
-        <v>370000</v>
+        <v>268400</v>
       </c>
       <c r="G41" s="3">
-        <v>356300</v>
+        <v>370200</v>
       </c>
       <c r="H41" s="3">
-        <v>370400</v>
+        <v>346300</v>
       </c>
       <c r="I41" s="3">
-        <v>323100</v>
+        <v>362300</v>
       </c>
       <c r="J41" s="3">
+        <v>333700</v>
+      </c>
+      <c r="K41" s="3">
         <v>210600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>291300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>286500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>320200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>367900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>361900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>338900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>335900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>217700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>234800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>171600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>204100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>321100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>431100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>165300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>204100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>166800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>61700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>61600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>88000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>167200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>74900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>145700</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI41" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>10</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>28200</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>10</v>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>38100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3757,8 +3847,8 @@
       <c r="P42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3814,674 +3904,695 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1475800</v>
+        <v>944400</v>
       </c>
       <c r="E43" s="3">
-        <v>1509500</v>
+        <v>908600</v>
       </c>
       <c r="F43" s="3">
-        <v>1418800</v>
+        <v>892000</v>
       </c>
       <c r="G43" s="3">
-        <v>1386400</v>
+        <v>1000500</v>
       </c>
       <c r="H43" s="3">
-        <v>1371500</v>
+        <v>759100</v>
       </c>
       <c r="I43" s="3">
-        <v>1376200</v>
+        <v>632100</v>
       </c>
       <c r="J43" s="3">
+        <v>610500</v>
+      </c>
+      <c r="K43" s="3">
         <v>1451900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1406500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1299400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1166100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1183700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1143300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1213000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1206900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1370400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1473600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1384300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1357000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1226000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1001000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>900300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>875300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>953400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>957000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1390300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1719200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1509000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1421400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1287700</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6300</v>
+        <v>6900</v>
       </c>
       <c r="E44" s="3">
-        <v>4200</v>
+        <v>6200</v>
       </c>
       <c r="F44" s="3">
-        <v>4700</v>
+        <v>4100</v>
       </c>
       <c r="G44" s="3">
-        <v>8100</v>
+        <v>14200</v>
       </c>
       <c r="H44" s="3">
-        <v>7700</v>
+        <v>7900</v>
       </c>
       <c r="I44" s="3">
-        <v>7200</v>
+        <v>7600</v>
       </c>
       <c r="J44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K44" s="3">
         <v>7600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>9700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>16400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>21400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>15800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>8500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>8300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>13300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>10600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>13600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>15100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>18900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>18500</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH44" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI44" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>863200</v>
+        <v>370200</v>
       </c>
       <c r="E45" s="3">
-        <v>899000</v>
+        <v>373600</v>
       </c>
       <c r="F45" s="3">
-        <v>786800</v>
+        <v>466600</v>
       </c>
       <c r="G45" s="3">
-        <v>868500</v>
+        <v>438000</v>
       </c>
       <c r="H45" s="3">
-        <v>877100</v>
+        <v>440000</v>
       </c>
       <c r="I45" s="3">
-        <v>1041500</v>
+        <v>455300</v>
       </c>
       <c r="J45" s="3">
+        <v>532900</v>
+      </c>
+      <c r="K45" s="3">
         <v>798700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>747300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>784900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>822800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>741600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>802100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>718700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>709200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>690800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1001300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1110800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1018200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>978100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>710400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>581500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>421600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>368100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>409800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>286300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>266700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>199200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>111500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>70400</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI45" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2640500</v>
+        <v>2599600</v>
       </c>
       <c r="E46" s="3">
-        <v>2685900</v>
+        <v>2577400</v>
       </c>
       <c r="F46" s="3">
-        <v>2608600</v>
+        <v>2638500</v>
       </c>
       <c r="G46" s="3">
-        <v>2619300</v>
+        <v>2609400</v>
       </c>
       <c r="H46" s="3">
-        <v>2626800</v>
+        <v>2546300</v>
       </c>
       <c r="I46" s="3">
-        <v>2748000</v>
+        <v>2569200</v>
       </c>
       <c r="J46" s="3">
+        <v>2837600</v>
+      </c>
+      <c r="K46" s="3">
         <v>2506900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2457100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2380100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2317100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2299800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2314800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2277100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2261600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2285400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2718400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2675000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2588000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2541600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2163900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1662800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1509400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1496600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1441900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1748800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2087400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1890500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1626700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1522300</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI46" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>112600</v>
+        <v>36000</v>
       </c>
       <c r="E47" s="3">
-        <v>115500</v>
+        <v>35200</v>
       </c>
       <c r="F47" s="3">
-        <v>148800</v>
+        <v>35300</v>
       </c>
       <c r="G47" s="3">
-        <v>187800</v>
+        <v>36000</v>
       </c>
       <c r="H47" s="3">
-        <v>209000</v>
+        <v>47700</v>
       </c>
       <c r="I47" s="3">
-        <v>200800</v>
+        <v>48200</v>
       </c>
       <c r="J47" s="3">
+        <v>50800</v>
+      </c>
+      <c r="K47" s="3">
         <v>199300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>195600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>185900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>144900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>145900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>168900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>183700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>194400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>198700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>197200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>212500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>249100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>297900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>310000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>258300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>248900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>272600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>253800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>314900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>349900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>268400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>218800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>194900</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI47" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>77300</v>
+        <v>82500</v>
       </c>
       <c r="E48" s="3">
-        <v>68200</v>
+        <v>75500</v>
       </c>
       <c r="F48" s="3">
-        <v>63000</v>
+        <v>67000</v>
       </c>
       <c r="G48" s="3">
-        <v>60300</v>
+        <v>67200</v>
       </c>
       <c r="H48" s="3">
-        <v>54300</v>
+        <v>58700</v>
       </c>
       <c r="I48" s="3">
-        <v>46100</v>
+        <v>53200</v>
       </c>
       <c r="J48" s="3">
+        <v>47600</v>
+      </c>
+      <c r="K48" s="3">
         <v>40100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>30100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8700</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>124200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>121100</v>
+      </c>
+      <c r="F49" s="3">
+        <v>123100</v>
+      </c>
+      <c r="G49" s="3">
+        <v>126500</v>
+      </c>
+      <c r="H49" s="3">
         <v>124100</v>
       </c>
-      <c r="E49" s="3">
-        <v>125300</v>
-      </c>
-      <c r="F49" s="3">
-        <v>126500</v>
-      </c>
-      <c r="G49" s="3">
-        <v>127700</v>
-      </c>
-      <c r="H49" s="3">
-        <v>128900</v>
-      </c>
       <c r="I49" s="3">
-        <v>130100</v>
+        <v>126100</v>
       </c>
       <c r="J49" s="3">
+        <v>134400</v>
+      </c>
+      <c r="K49" s="3">
         <v>131300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>129900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>131900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>133100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>133400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>138500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>139800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>142500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>139300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>148700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>150000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>161900</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>10</v>
       </c>
@@ -4494,8 +4605,8 @@
       <c r="Z49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>290800</v>
+        <v>96200</v>
       </c>
       <c r="E52" s="3">
-        <v>288300</v>
+        <v>98700</v>
       </c>
       <c r="F52" s="3">
-        <v>315600</v>
+        <v>106100</v>
       </c>
       <c r="G52" s="3">
-        <v>347200</v>
+        <v>137700</v>
       </c>
       <c r="H52" s="3">
-        <v>349100</v>
+        <v>179200</v>
       </c>
       <c r="I52" s="3">
-        <v>342700</v>
+        <v>186000</v>
       </c>
       <c r="J52" s="3">
+        <v>190100</v>
+      </c>
+      <c r="K52" s="3">
         <v>332500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>333600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>339300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>320600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>297300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>279600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>241400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>202900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>191200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>183300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>176700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>177400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>108200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>98300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>67800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>54000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>29900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>42900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>38800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>18600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>17700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>12400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8400</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI52" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3245300</v>
+        <v>3211200</v>
       </c>
       <c r="E54" s="3">
-        <v>3283100</v>
+        <v>3167700</v>
       </c>
       <c r="F54" s="3">
-        <v>3262400</v>
+        <v>3225300</v>
       </c>
       <c r="G54" s="3">
-        <v>3342300</v>
+        <v>3263400</v>
       </c>
       <c r="H54" s="3">
-        <v>3368200</v>
+        <v>3249200</v>
       </c>
       <c r="I54" s="3">
-        <v>3467700</v>
+        <v>3294300</v>
       </c>
       <c r="J54" s="3">
+        <v>3580800</v>
+      </c>
+      <c r="K54" s="3">
         <v>3210200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3149800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3067300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2945600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2903300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2924100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2860800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2819200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2832000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3262900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3229800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3192300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2962000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2586100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2003200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1826400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1811100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1749600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2113200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2466200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2186000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1866600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1734300</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI54" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,588 +5230,604 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="M57" s="3">
+        <v>8400</v>
+      </c>
+      <c r="N57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="O57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="R57" s="3">
         <v>6100</v>
       </c>
-      <c r="E57" s="3">
-        <v>4700</v>
-      </c>
-      <c r="F57" s="3">
-        <v>7000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>5600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>5200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>4600</v>
-      </c>
-      <c r="L57" s="3">
-        <v>8400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>3500</v>
-      </c>
-      <c r="N57" s="3">
-        <v>2200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>2700</v>
-      </c>
-      <c r="P57" s="3">
-        <v>5300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>6100</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>31100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>31800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>38800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>21900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>19700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>29800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>27100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>18600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>29400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11700</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>416400</v>
+        <v>502600</v>
       </c>
       <c r="E58" s="3">
-        <v>442700</v>
+        <v>406500</v>
       </c>
       <c r="F58" s="3">
-        <v>633100</v>
+        <v>434900</v>
       </c>
       <c r="G58" s="3">
-        <v>767900</v>
+        <v>639100</v>
       </c>
       <c r="H58" s="3">
-        <v>817300</v>
+        <v>746500</v>
       </c>
       <c r="I58" s="3">
-        <v>1101900</v>
+        <v>799400</v>
       </c>
       <c r="J58" s="3">
+        <v>1137800</v>
+      </c>
+      <c r="K58" s="3">
         <v>1073800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1002500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>648600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>571500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>676700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>699600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>755800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>912700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>906600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1003500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1045300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1007500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>882800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>701900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>657800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>605900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>738400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>951600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1402200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1893600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1587100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1618800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1541700</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1065800</v>
+        <v>344600</v>
       </c>
       <c r="E59" s="3">
-        <v>1109700</v>
+        <v>379700</v>
       </c>
       <c r="F59" s="3">
-        <v>1097400</v>
+        <v>427200</v>
       </c>
       <c r="G59" s="3">
-        <v>1008700</v>
+        <v>963500</v>
       </c>
       <c r="H59" s="3">
-        <v>846300</v>
+        <v>426300</v>
       </c>
       <c r="I59" s="3">
-        <v>758800</v>
+        <v>354500</v>
       </c>
       <c r="J59" s="3">
+        <v>323600</v>
+      </c>
+      <c r="K59" s="3">
         <v>682200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>666200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>665700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>696400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>727700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>721300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>719300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>680900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>760500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1045100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1055700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1077900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>595500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>535200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>442300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>415200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>406500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>321700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>293700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>242300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>292200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>186800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>158000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI59" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1488300</v>
+        <v>1561500</v>
       </c>
       <c r="E60" s="3">
-        <v>1557100</v>
+        <v>1452700</v>
       </c>
       <c r="F60" s="3">
-        <v>1737500</v>
+        <v>1529600</v>
       </c>
       <c r="G60" s="3">
-        <v>1778700</v>
+        <v>1738100</v>
       </c>
       <c r="H60" s="3">
-        <v>1669300</v>
+        <v>1729100</v>
       </c>
       <c r="I60" s="3">
-        <v>1865900</v>
+        <v>1632600</v>
       </c>
       <c r="J60" s="3">
+        <v>1926700</v>
+      </c>
+      <c r="K60" s="3">
         <v>1759700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1673400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1322600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1271400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1406600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1423600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1480400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1599700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1673100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2058300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2109800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2100300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1509400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1269000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1138900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1043000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1164600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1303200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1723000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2154400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1908700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1815300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1711400</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI60" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>317700</v>
+        <v>152400</v>
       </c>
       <c r="E61" s="3">
-        <v>309100</v>
+        <v>316600</v>
       </c>
       <c r="F61" s="3">
-        <v>138200</v>
+        <v>310300</v>
       </c>
       <c r="G61" s="3">
-        <v>169200</v>
+        <v>145400</v>
       </c>
       <c r="H61" s="3">
-        <v>362600</v>
+        <v>171500</v>
       </c>
       <c r="I61" s="3">
-        <v>310900</v>
+        <v>362500</v>
       </c>
       <c r="J61" s="3">
+        <v>334500</v>
+      </c>
+      <c r="K61" s="3">
         <v>209300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>299600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>578700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>507700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>356200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>371700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>358500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>308400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>382200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>469300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>440800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>441600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>384400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>338000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>32100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>22900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>52200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>47300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>24800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>19900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5000</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>16700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>15800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>17800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>16800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>14900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>20200</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K62" s="3">
         <v>21900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>52000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>51700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>42600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>33400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>27200</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5697,8 +5843,8 @@
       <c r="AF62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
+      <c r="AG62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH62" s="3">
         <v>0</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1822700</v>
+        <v>1725100</v>
       </c>
       <c r="E66" s="3">
-        <v>1882000</v>
+        <v>1779100</v>
       </c>
       <c r="F66" s="3">
-        <v>1893500</v>
+        <v>1848900</v>
       </c>
       <c r="G66" s="3">
-        <v>1964700</v>
+        <v>1894100</v>
       </c>
       <c r="H66" s="3">
-        <v>2046700</v>
+        <v>1909900</v>
       </c>
       <c r="I66" s="3">
-        <v>2197000</v>
+        <v>2001800</v>
       </c>
       <c r="J66" s="3">
+        <v>2268600</v>
+      </c>
+      <c r="K66" s="3">
         <v>1990900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2000800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1936500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1817100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1794800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1827100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1852900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1921300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2067700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2537800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2562200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2551900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1945800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1658700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1185500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1108400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1214700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1355400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1770300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2189700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1933500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1835100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1716400</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI66" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6436,22 +6604,25 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
         <v>100100</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>97600</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1013600</v>
+        <v>1070100</v>
       </c>
       <c r="E72" s="3">
-        <v>993700</v>
+        <v>989400</v>
       </c>
       <c r="F72" s="3">
-        <v>965300</v>
+        <v>976200</v>
       </c>
       <c r="G72" s="3">
-        <v>982700</v>
+        <v>965600</v>
       </c>
       <c r="H72" s="3">
-        <v>930500</v>
+        <v>955300</v>
       </c>
       <c r="I72" s="3">
-        <v>880300</v>
+        <v>910100</v>
       </c>
       <c r="J72" s="3">
+        <v>909000</v>
+      </c>
+      <c r="K72" s="3">
         <v>834200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>775800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>742400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>719500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>703800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>688200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>605600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>499000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>384600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>332100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>281300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>235000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>629300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>549500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>443800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>361300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>260300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>74600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>30400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-35600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-58600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-72800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-82900</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI72" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1422600</v>
+        <v>1486100</v>
       </c>
       <c r="E76" s="3">
-        <v>1401100</v>
+        <v>1388600</v>
       </c>
       <c r="F76" s="3">
-        <v>1368900</v>
+        <v>1376400</v>
       </c>
       <c r="G76" s="3">
-        <v>1377600</v>
+        <v>1369400</v>
       </c>
       <c r="H76" s="3">
-        <v>1321500</v>
+        <v>1339200</v>
       </c>
       <c r="I76" s="3">
-        <v>1270800</v>
+        <v>1292500</v>
       </c>
       <c r="J76" s="3">
+        <v>1312200</v>
+      </c>
+      <c r="K76" s="3">
         <v>1219300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1149000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1130800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1128400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1108500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1097000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1007800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>898000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>764300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>725000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>667500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>640500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1016200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>927400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>817700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>718000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>596400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>394200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>342900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>276500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>252500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-68600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-79700</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AI76" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>31900</v>
+        <v>44100</v>
       </c>
       <c r="E81" s="3">
-        <v>28400</v>
+        <v>31200</v>
       </c>
       <c r="F81" s="3">
+        <v>27900</v>
+      </c>
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
-        <v>52300</v>
-      </c>
       <c r="H81" s="3">
-        <v>50200</v>
+        <v>50800</v>
       </c>
       <c r="I81" s="3">
-        <v>46200</v>
+        <v>49100</v>
       </c>
       <c r="J81" s="3">
+        <v>47700</v>
+      </c>
+      <c r="K81" s="3">
         <v>42500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>38100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>22900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>35300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>82500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>111800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>102200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>70900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>50800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>61700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-107000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>79700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>111500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>98000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>64500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>152400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>62600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>92900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>25500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>800</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH81" s="3">
         <v>800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7485,11 +7684,11 @@
         <v>0</v>
       </c>
       <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
         <v>800</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>10</v>
       </c>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,31 +8221,34 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -8091,11 +8308,11 @@
         <v>0</v>
       </c>
       <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>99300</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>10</v>
       </c>
@@ -8108,8 +8325,11 @@
       <c r="AI89" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8365,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8229,11 +8450,11 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-800</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>10</v>
       </c>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,31 +8675,34 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8532,11 +8762,11 @@
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-187300</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>10</v>
       </c>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,31 +9233,34 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -9074,11 +9320,11 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>180500</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>10</v>
       </c>
@@ -9091,31 +9337,34 @@
       <c r="AI100" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9175,11 +9424,11 @@
         <v>0</v>
       </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-200</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF101" s="3" t="s">
         <v>10</v>
       </c>
@@ -9192,31 +9441,34 @@
       <c r="AI101" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -9276,11 +9528,11 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>92300</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>10</v>
       </c>
@@ -9291,6 +9543,9 @@
         <v>10</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>LX</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>501300</v>
+      </c>
+      <c r="E8" s="3">
         <v>522100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>501000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>449000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>494900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>480900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>421400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>434200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>430000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>371700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>335400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>238100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>303700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>422000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>464700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>422800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>422200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>464800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>435900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>394400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>484700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>490900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>388900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>269900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>370200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>258900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>285400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>231500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>236500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>215600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>195500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>177200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>202100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E9" s="3">
         <v>81100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>81700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>51600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>74000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>71500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>84300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>88100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>282900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>247700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>247400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>174000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>136300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>207900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>228500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>226200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>210600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>320600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>293300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>368100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>257200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>229000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>217500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>160900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>173000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>151500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>164000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>166700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>182200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>165500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>154200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>137800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>167000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>125700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>195600</v>
+      </c>
+      <c r="E10" s="3">
         <v>206900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>206800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>188700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>206000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>207700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>154500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>152200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>147100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>124000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>88000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>64100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>167400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>214200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>236200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>196600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>211600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>144100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>142600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>26300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>227500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>261900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>171400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>109000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>197200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>107400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>121500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>64800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>54300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>50100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>41200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>39400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>35200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E12" s="3">
         <v>21200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>18900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>19400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>21500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>21200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>18500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>17400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>15600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>18600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>15600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>14300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>11600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>13100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>11000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>19900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>10000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,70 +1377,73 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3">
         <v>42600</v>
-      </c>
-      <c r="H14" s="3">
-        <v>100</v>
       </c>
       <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="3">
         <v>4700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1436,23 +1455,23 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1500</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>700</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3">
         <v>100</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1460,40 +1479,43 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>800</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E15" s="3">
         <v>3800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3600</v>
       </c>
       <c r="F15" s="3">
         <v>3600</v>
       </c>
       <c r="G15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H15" s="3">
         <v>3700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3300</v>
       </c>
       <c r="I15" s="3">
         <v>3300</v>
       </c>
       <c r="J15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K15" s="3">
         <v>3500</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>424100</v>
+      </c>
+      <c r="E17" s="3">
         <v>446300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>413300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>372200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>412500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>380400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>376600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>399800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>375400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>340200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>351000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>261600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>220400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>310600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>334500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>312400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>293800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>411400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>378100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>443700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>371300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>343000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>296900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>218100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>227900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>193700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>205600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>199500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>206600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>199300</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI17" s="3">
         <v>163100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>195600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>147300</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E18" s="3">
         <v>75800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>87700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>76800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>82400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>100500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>44700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>34500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>54700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>31500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>83200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>111500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>130100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>110300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>128400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>53400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>57800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-49300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>113400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>147900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>92000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>51800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>142200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>65200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>79800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>32000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>29900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>16300</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI18" s="3">
         <v>14100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,139 +1882,143 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E20" s="3">
         <v>20400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>48500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>40900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>38000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>31900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-18600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-24600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>16400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>44400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>37500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-41400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>10600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-44300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>15300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-77400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-18900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-17300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>22600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>26100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>41600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>7600</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI20" s="3">
         <v>2100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E21" s="3">
         <v>59100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>42800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>48100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>71900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>66600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>62500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>10</v>
       </c>
@@ -2040,53 +2076,56 @@
       <c r="AD21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF21" s="3">
         <v>33000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>400</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -2111,8 +2150,8 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>10</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>10</v>
@@ -2129,249 +2168,258 @@
       <c r="Y22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA22" s="3">
         <v>400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E23" s="3">
         <v>54400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>35300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>66600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>60200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>52700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>47900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>28900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>41800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>97600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>133300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>121000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>84100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>57400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>73000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-126700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>94500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>130600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>114600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>77600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>183200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>73000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>78200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>31500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>31100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>20400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>13100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E24" s="3">
         <v>10300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>18900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>13100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-19700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>14800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>19100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>30700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>10500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>16200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4900</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>4700</v>
       </c>
       <c r="AJ24" s="3">
         <v>4700</v>
       </c>
+      <c r="AK24" s="3">
+        <v>4700</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E26" s="3">
         <v>44100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>50800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>49100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>47700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>42500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>38100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>35300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>82600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>111800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>102100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>70900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>50800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>61700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-107000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>79700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>111500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>98000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>64500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>152400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>62600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>92900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>25500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>14900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>10100</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI26" s="3">
         <v>8200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E27" s="3">
         <v>44100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>31200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>50800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>49100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>47700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>42500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>38100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>82500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>111800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>102200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>70900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>50800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>61700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-107000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>79700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>111500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>98000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>64500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>152400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>62600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>92900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>25500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>800</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI27" s="3">
         <v>800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-20400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-48500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-40900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-38000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-31900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>18600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>24600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-16400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-44400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-37500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>41400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-10600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>44300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-15300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>77400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>18900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>17300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-22600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-26100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-41600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E33" s="3">
         <v>44100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>50800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>49100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>47700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>42500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>38100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>82500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>111800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>102200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>70900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>50800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>61700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-107000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>79700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>111500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>98000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>64500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>152400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>62600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>92900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>25500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>800</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI33" s="3">
         <v>800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E35" s="3">
         <v>44100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>50800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>49100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>47700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>42500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>38100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>82500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>111800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>102200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>70900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>50800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>61700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-107000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>79700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>111500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>98000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>64500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>152400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>62600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>92900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>25500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>800</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI35" s="3">
         <v>800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>308800</v>
+      </c>
+      <c r="E41" s="3">
         <v>307000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>288100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>268400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>370200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>346300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>362300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>333700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>210600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>291300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>286500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>320200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>367900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>361900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>338900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>335900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>217700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>234800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>171600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>204100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>321100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>431100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>165300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>204100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>166800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>61700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>61600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>88000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>167200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>74900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>145700</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3818,11 +3907,11 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>28200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -3830,11 +3919,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>38100</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3850,8 +3939,8 @@
       <c r="Q42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3907,695 +3996,716 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>754900</v>
+      </c>
+      <c r="E43" s="3">
         <v>944400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>908600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>892000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1000500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>759100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>632100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>610500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1451900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1406500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1299400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1166100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1183700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1143300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1213000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1206900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1370400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1473600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1384300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1357000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1226000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1001000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>900300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>875300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>953400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>957000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1390300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1719200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1509000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1421400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1287700</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E44" s="3">
         <v>6900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>16400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>21400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>15800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>8500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>8300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>13300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>10600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>13600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>15100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>18900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>18500</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI44" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ44" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>370200</v>
+        <v>522700</v>
       </c>
       <c r="E45" s="3">
+        <v>572100</v>
+      </c>
+      <c r="F45" s="3">
         <v>373600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>466600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>438000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>440000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>455300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>532900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>798700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>747300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>784900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>822800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>741600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>802100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>718700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>709200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>690800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1001300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1110800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1018200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>978100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>710400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>581500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>421600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>368100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>409800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>286300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>266700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>199200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>111500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>70400</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ45" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2453600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2599600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2577400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2638500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2609400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2546300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2569200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2837600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2506900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2457100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2380100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2317100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2299800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2314800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2277100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2261600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2285400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2718400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2675000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2588000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2541600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2163900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1662800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1509400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1496600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1441900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1748800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2087400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1890500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1626700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1522300</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ46" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E47" s="3">
         <v>36000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>35200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>35300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>36000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>47700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>48200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>50800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>199300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>195600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>185900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>144900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>145900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>168900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>183700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>194400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>198700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>197200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>212500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>249100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>297900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>310000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>258300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>248900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>272600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>253800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>314900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>349900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>268400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>218800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>194900</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI47" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ47" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E48" s="3">
         <v>82500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>75500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>67000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>67200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>58700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>53200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>47600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>30100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8700</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E49" s="3">
         <v>124200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>121100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>123100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>126500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>124100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>126100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>134400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>131300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>129900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>131900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>133100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>133400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>138500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>139800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>142500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>139300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>148700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>150000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>161900</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>10</v>
       </c>
@@ -4608,8 +4718,8 @@
       <c r="AA49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>82400</v>
+      </c>
+      <c r="E52" s="3">
         <v>96200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>98700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>106100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>137700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>179200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>186000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>190100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>332500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>333600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>339300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>320600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>297300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>279600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>241400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>202900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>191200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>183300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>176700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>177400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>108200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>98300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>67800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>54000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>29900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>42900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>38800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>18600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>17700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8400</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3047100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3211200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3167700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3225300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3263400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3249200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3294300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3580800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3210200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3149800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3067300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2945600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2903300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2924100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2860800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2819200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2832000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3262900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3229800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3192300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2962000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2586100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2003200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1826400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1811100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1749600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2113200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2466200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2186000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1866600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1734300</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ54" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,528 +5360,544 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>31100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>31800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>38800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>21900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>19700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>29800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>27100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>18600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>29400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11700</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ57" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E58" s="3">
         <v>502600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>406500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>434900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>639100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>746500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>799400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1137800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1073800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1002500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>648600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>571500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>676700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>699600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>755800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>912700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>906600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1003500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1045300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1007500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>882800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>701900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>657800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>605900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>738400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>951600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1402200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1893600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1587100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1618800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1541700</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI58" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ58" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>282900</v>
+      </c>
+      <c r="E59" s="3">
         <v>344600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>379700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>427200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>963500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>426300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>354500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>323600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>682200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>666200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>665700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>696400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>727700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>721300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>719300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>680900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>760500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1045100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1055700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1077900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>595500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>535200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>442300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>415200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>406500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>321700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>293700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>242300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>292200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>186800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>158000</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1315800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1561500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1452700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1529600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1738100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1729100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1632600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1926700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1759700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1673400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1322600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1271400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1406600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1423600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1480400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1599700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1673100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2058300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2109800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2100300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1509400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1269000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1138900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1043000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1164600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1303200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1723000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2154400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1908700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1815300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1711400</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ60" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>247300</v>
+      </c>
+      <c r="E61" s="3">
         <v>152400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>316600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>310300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>145400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>171500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>362500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>334500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>209300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>299600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>578700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>507700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>356200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>371700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>358500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>308400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>382200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>469300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>440800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>441600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>384400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>338000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>22900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>52200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>47300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>24800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>19900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5000</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,60 +5922,60 @@
       <c r="J62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L62" s="3">
         <v>21900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>10300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>52000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>51700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>42600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>33400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>27200</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5846,8 +5991,8 @@
       <c r="AG62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH62" s="3">
-        <v>0</v>
+      <c r="AH62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AI62" s="3">
         <v>0</v>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1575600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1725100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1779100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1848900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1894100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1909900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2001800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2268600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1990900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2000800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1936500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1817100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1794800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1827100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1852900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1921300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2067700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2537800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2562200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2551900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1945800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1658700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1185500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1108400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1214700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1355400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1770300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2189700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1933500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1835100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1716400</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ66" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6607,22 +6774,25 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>100100</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>97600</v>
       </c>
-      <c r="AH70" s="3">
-        <v>0</v>
-      </c>
       <c r="AI70" s="3">
         <v>0</v>
       </c>
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1066300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1070100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>989400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>976200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>965600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>955300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>910100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>909000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>834200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>775800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>742400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>719500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>703800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>688200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>605600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>499000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>384600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>332100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>281300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>235000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>629300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>549500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>443800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>361300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>260300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>74600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>30400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-35600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-58600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-72800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-82900</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ72" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1471400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1486100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1388600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1376400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1369400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1339200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1292500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1312200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1219300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1149000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1130800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1128400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1108500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1097000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1007800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>898000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>764300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>725000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>667500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>640500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1016200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>927400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>817700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>718000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>596400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>394200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>342900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>276500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>252500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-68600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-79700</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AJ76" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E81" s="3">
         <v>44100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>50800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>49100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>47700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>42500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>38100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>82500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>111800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>102200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>70900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>50800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>61700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-107000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>79700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>111500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>98000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>64500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>152400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>62600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>92900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>25500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>800</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI81" s="3">
         <v>800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7626,8 +7824,8 @@
       <c r="J83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7687,11 +7885,11 @@
         <v>0</v>
       </c>
       <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
         <v>800</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>10</v>
       </c>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,8 +8437,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8250,8 +8466,8 @@
       <c r="J89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -8311,11 +8527,11 @@
         <v>0</v>
       </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>99300</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>10</v>
       </c>
@@ -8328,8 +8544,11 @@
       <c r="AJ89" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8392,8 +8612,8 @@
       <c r="J91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8453,11 +8673,11 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-800</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>10</v>
       </c>
@@ -8470,8 +8690,11 @@
       <c r="AJ91" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,8 +8904,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8704,8 +8933,8 @@
       <c r="J94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8765,11 +8994,11 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-187300</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>10</v>
       </c>
@@ -8782,8 +9011,11 @@
       <c r="AJ94" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,8 +9478,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9262,8 +9507,8 @@
       <c r="J100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9323,11 +9568,11 @@
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>180500</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>10</v>
       </c>
@@ -9340,8 +9585,11 @@
       <c r="AJ100" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9427,11 +9675,11 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-200</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG101" s="3" t="s">
         <v>10</v>
       </c>
@@ -9444,8 +9692,11 @@
       <c r="AJ101" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK101" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9470,8 +9721,8 @@
       <c r="J102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -9531,11 +9782,11 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>92300</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>10</v>
       </c>
@@ -9546,6 +9797,9 @@
         <v>10</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
@@ -1493,7 +1493,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="E15" s="3">
         <v>3800</v>
@@ -1996,7 +1996,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>63000</v>
+        <v>63200</v>
       </c>
       <c r="E21" s="3">
         <v>59100</v>
@@ -3898,7 +3898,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -4005,7 +4005,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>754900</v>
+        <v>899700</v>
       </c>
       <c r="E43" s="3">
         <v>944400</v>
@@ -4112,7 +4112,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>3100</v>
+        <v>11700</v>
       </c>
       <c r="E44" s="3">
         <v>6900</v>
@@ -4219,7 +4219,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>522700</v>
+        <v>358200</v>
       </c>
       <c r="E45" s="3">
         <v>572100</v>
@@ -4552,7 +4552,7 @@
         <v>67000</v>
       </c>
       <c r="H48" s="3">
-        <v>67200</v>
+        <v>63000</v>
       </c>
       <c r="I48" s="3">
         <v>58700</v>
@@ -4980,7 +4980,7 @@
         <v>106100</v>
       </c>
       <c r="H52" s="3">
-        <v>137700</v>
+        <v>141900</v>
       </c>
       <c r="I52" s="3">
         <v>179200</v>
@@ -5474,7 +5474,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>472000</v>
+        <v>477400</v>
       </c>
       <c r="E58" s="3">
         <v>502600</v>
@@ -5581,7 +5581,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>282900</v>
+        <v>666300</v>
       </c>
       <c r="E59" s="3">
         <v>344600</v>

--- a/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
   <si>
     <t>LX</t>
   </si>
@@ -656,479 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3">
+        <v>427800</v>
+      </c>
+      <c r="F8" s="3">
         <v>501300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>522100</v>
       </c>
-      <c r="F8" s="3">
-        <v>501000</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3">
         <v>449000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>494900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>480900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>421400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>434200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>430000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>371700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>335400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>238100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>303700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>422000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>464700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>422800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>422200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>464800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>435900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>394400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>484700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>490900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>388900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>269900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>370200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>258900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>285400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>231500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>236500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>215600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>195500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>177200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>202100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>155000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3">
+        <v>61200</v>
+      </c>
+      <c r="F9" s="3">
         <v>89000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>81100</v>
       </c>
-      <c r="F9" s="3">
-        <v>81700</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="3">
         <v>51600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>74000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>71500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>84300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>88100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>282900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>247700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>247400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>174000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>136300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>207900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>228500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>226200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>210600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>320600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>293300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>368100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>257200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>229000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>217500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>160900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>173000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>151500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>164000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>166700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>182200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>165500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>154200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>137800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>167000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>125700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3">
+        <v>185800</v>
+      </c>
+      <c r="F10" s="3">
         <v>195600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>206900</v>
       </c>
-      <c r="F10" s="3">
-        <v>206800</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="3">
         <v>188700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>206000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>207700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>154500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>152200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>147100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>124000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>88000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>64100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>167400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>214200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>236200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>196600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>211600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>144100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>142600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>26300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>227500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>261900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>171400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>109000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>197200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>107400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>121500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>64800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>54300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>50100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>41200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>39400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>35200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,115 +1192,123 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F12" s="3">
         <v>20700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>21200</v>
       </c>
-      <c r="F12" s="3">
-        <v>19700</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3">
         <v>18700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>19200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>17300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>16700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>18900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>19100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>19400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>21500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>21200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>22600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>18600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>18500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>17800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>13200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>17400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>19800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>19900</v>
-      </c>
-      <c r="X12" s="3">
-        <v>15600</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>18600</v>
       </c>
       <c r="Z12" s="3">
         <v>15600</v>
       </c>
       <c r="AA12" s="3">
+        <v>18600</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>15600</v>
+      </c>
+      <c r="AC12" s="3">
         <v>14300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>11600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>13100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>11000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>9800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>19900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>10000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>8500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>6600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,76 +1414,82 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3">
         <v>42600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V14" s="3">
         <v>4700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>5200</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1458,70 +1498,76 @@
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1500</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>700</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="3">
         <v>100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>800</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>3800</v>
       </c>
       <c r="F15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>3600</v>
       </c>
-      <c r="G15" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>3700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>3300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>3300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>3500</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1640,14 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1682,236 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3">
+        <v>363100</v>
+      </c>
+      <c r="F17" s="3">
         <v>424100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>446300</v>
       </c>
-      <c r="F17" s="3">
-        <v>413300</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="3">
         <v>372200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>412500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>380400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>376600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>399800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>375400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>340200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>351000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>261600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>220400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>310600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>334500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>312400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>293800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>411400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>378100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>443700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>371300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>343000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>296900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>218100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>227900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>193700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>205600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>199500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>206600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>199300</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK17" s="3">
         <v>163100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>195600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>147300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3">
+        <v>64700</v>
+      </c>
+      <c r="F18" s="3">
         <v>77200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>75800</v>
       </c>
-      <c r="F18" s="3">
-        <v>87700</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="3">
         <v>76800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>82400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>100500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>44700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>34500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>54700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>31500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-15600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-23500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>83200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>111500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>130100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>110300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>128400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>53400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>57800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-49300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>113400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>147900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>92000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>51800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>142200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>65200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>79800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>32000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>29900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>16300</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK18" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>6500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,148 +1949,156 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F20" s="3">
         <v>17800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>20400</v>
       </c>
-      <c r="F20" s="3">
-        <v>48500</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="3">
         <v>40900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>38000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>31900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-18600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-24600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>16400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>44400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>37500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-41400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-13800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>3200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>10600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-44300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>15300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-77400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-18900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-17300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>22600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>26100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>41600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>9000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>2300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>7600</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK20" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>79300</v>
+      </c>
+      <c r="F21" s="3">
         <v>63200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>59100</v>
       </c>
-      <c r="F21" s="3">
-        <v>42800</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>39500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>48100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>71900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>66600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>62500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>10</v>
       </c>
@@ -2079,59 +2153,65 @@
       <c r="AE21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH21" s="3">
         <v>33000</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL21" s="3">
         <v>6600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>400</v>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="3">
+        <v>400</v>
       </c>
       <c r="G22" s="3">
+        <v>600</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>3000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -2153,11 +2233,11 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>10</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>10</v>
@@ -2171,255 +2251,273 @@
       <c r="Z22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC22" s="3">
         <v>400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>1200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>1000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>1100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>3600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>3300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>3000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="3">
+        <v>73200</v>
+      </c>
+      <c r="F23" s="3">
         <v>59000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>54400</v>
       </c>
-      <c r="F23" s="3">
-        <v>39400</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="3">
         <v>35300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>66600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>60200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>58500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>52700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>47900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>28900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>14000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>41800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>97600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>133300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>121000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>84100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>57400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>73000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-126700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>94500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>130600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>114600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>77600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>183200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>73000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>78200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>31500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>31100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>20400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>5600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>13100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>2900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F24" s="3">
         <v>9300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>10300</v>
       </c>
-      <c r="F24" s="3">
-        <v>8300</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3">
         <v>7400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>15800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>11100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>10800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>10200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>9800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>5600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>6500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>15100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>21500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>18900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>13100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>6600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>11300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-19700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>14800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>19100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>16600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>13000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>30700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>10500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>5900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>16200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>10300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>3300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>4700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2623,240 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F26" s="3">
         <v>49700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>44100</v>
       </c>
-      <c r="F26" s="3">
-        <v>31200</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="3">
         <v>27900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>50800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>49100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>47700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>42500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>38100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>23300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>11300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>35300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>82600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>111800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>102100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>70900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>50800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>61700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-107000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>79700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>111500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>98000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>64500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>152400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>62600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>92900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>25500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>14900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>10100</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK26" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F27" s="3">
         <v>49700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>44100</v>
       </c>
-      <c r="F27" s="3">
-        <v>31200</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="3">
         <v>27900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>50800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>49100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>47700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>42500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>38100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>22900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>10900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>35300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>82500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>111800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>102200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>70900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>50800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>61700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-107000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>79700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>111500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>98000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>64500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>152400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>62600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>92900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>25500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>3200</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>800</v>
-      </c>
-      <c r="AH27" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI27" s="3">
         <v>800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AJ27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AL27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2962,14 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3075,14 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3188,14 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3301,240 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-17800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-20400</v>
       </c>
-      <c r="F32" s="3">
-        <v>-48500</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="3">
         <v>-40900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-38000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-31900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>18600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>24600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-16400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-44400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-37500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>41400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>13800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-3200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-10600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>44300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-15300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>77400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>18900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>17300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-22600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-41600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F33" s="3">
         <v>49700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>44100</v>
       </c>
-      <c r="F33" s="3">
-        <v>31200</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="3">
         <v>27900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>50800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>49100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>47700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>42500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>38100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>22900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>10900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>35300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>82500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>111800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>102200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>70900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>50800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>61700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-107000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>79700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>111500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>98000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>64500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>152400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>62600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>92900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>25500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>3200</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>800</v>
-      </c>
-      <c r="AH33" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI33" s="3">
         <v>800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AJ33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AL33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3640,245 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F35" s="3">
         <v>49700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>44100</v>
       </c>
-      <c r="F35" s="3">
-        <v>31200</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="3">
         <v>27900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>50800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>49100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>47700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>42500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>38100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>22900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>10900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>35300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>82500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>111800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>102200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>70900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>50800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>61700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-107000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>79700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>111500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>98000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>64500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>152400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>62600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>92900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>25500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>3200</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>800</v>
-      </c>
-      <c r="AH35" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI35" s="3">
         <v>800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AJ35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AL35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3916,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,151 +3957,159 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="3">
+        <v>437300</v>
+      </c>
+      <c r="F41" s="3">
         <v>308800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>307000</v>
       </c>
-      <c r="F41" s="3">
-        <v>288100</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" s="3">
         <v>268400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>370200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>346300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>362300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>333700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>210600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>291300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>286500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>320200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>367900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>361900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>338900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>335900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>217700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>234800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>171600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>204100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>321100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>431100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>165300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>204100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>166800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>61700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>61600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>88000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>167200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>74900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>145700</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM41" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>11000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>28200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>38100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3942,11 +4122,11 @@
       <c r="R42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3999,719 +4179,761 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="3">
+        <v>701000</v>
+      </c>
+      <c r="F43" s="3">
         <v>899700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>944400</v>
       </c>
-      <c r="F43" s="3">
-        <v>908600</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="3">
         <v>892000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1000500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>759100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>632100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>610500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1451900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1406500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1299400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1166100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1183700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1143300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1213000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1206900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1370400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1473600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1384300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1357000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1226000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1001000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>900300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>875300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>953400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>957000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1390300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>1719200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1509000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>1421400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>1287700</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM43" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F44" s="3">
         <v>11700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6900</v>
       </c>
-      <c r="F44" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3">
         <v>4100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>14200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>7900</v>
-      </c>
-      <c r="J44" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K44" s="3">
-        <v>7400</v>
       </c>
       <c r="L44" s="3">
         <v>7600</v>
       </c>
       <c r="M44" s="3">
+        <v>7400</v>
+      </c>
+      <c r="N44" s="3">
+        <v>7600</v>
+      </c>
+      <c r="O44" s="3">
         <v>12000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>9400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>7900</v>
-      </c>
-      <c r="P44" s="3">
-        <v>6600</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>7500</v>
       </c>
       <c r="R44" s="3">
         <v>6600</v>
       </c>
       <c r="S44" s="3">
-        <v>9700</v>
+        <v>7500</v>
       </c>
       <c r="T44" s="3">
         <v>6600</v>
       </c>
       <c r="U44" s="3">
-        <v>8700</v>
+        <v>9700</v>
       </c>
       <c r="V44" s="3">
-        <v>8200</v>
+        <v>6600</v>
       </c>
       <c r="W44" s="3">
         <v>8700</v>
       </c>
       <c r="X44" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>8700</v>
+      </c>
+      <c r="Z44" s="3">
         <v>16400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>21400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>15800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>8500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>8300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>13300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>10600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>13600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>15100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>18900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>18500</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ44" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK44" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM44" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3">
+        <v>333700</v>
+      </c>
+      <c r="F45" s="3">
         <v>358200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>572100</v>
       </c>
-      <c r="F45" s="3">
-        <v>373600</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3">
         <v>466600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>438000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>440000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>455300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>532900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>798700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>747300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>784900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>822800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>741600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>802100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>718700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>709200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>690800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1001300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1110800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1018200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>978100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>710400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>581500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>421600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>368100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>409800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>286300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>266700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>199200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>111500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>70400</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM45" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2527000</v>
+      </c>
+      <c r="F46" s="3">
         <v>2453600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2599600</v>
       </c>
-      <c r="F46" s="3">
-        <v>2577400</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I46" s="3">
         <v>2638500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2609400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2546300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2569200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2837600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2506900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2457100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2380100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2317100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2299800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2314800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2277100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2261600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2285400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2718400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2675000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2588000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2541600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2163900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1662800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1509400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1496600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1441900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1748800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>2087400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1890500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1626700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>1522300</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM46" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3">
+        <v>33700</v>
+      </c>
+      <c r="F47" s="3">
         <v>38900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>36000</v>
       </c>
-      <c r="F47" s="3">
-        <v>35200</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3">
         <v>35300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>36000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>47700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>48200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>50800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>199300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>195600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>185900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>144900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>145900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>168900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>183700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>194400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>198700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>197200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>212500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>249100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>297900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>310000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>258300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>248900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>272600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>253800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>314900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>349900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>268400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>218800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>194900</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK47" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM47" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="3">
+        <v>87800</v>
+      </c>
+      <c r="F48" s="3">
         <v>84000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>82500</v>
       </c>
-      <c r="F48" s="3">
-        <v>75500</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" s="3">
         <v>67000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>63000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>58700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>53200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>47600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>40100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>33500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>30100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>29800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>27000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>22300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>18800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>17800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>17500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>15300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>15600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>15900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>14300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>13800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>14400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>14100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>12000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>11000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>10700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>10200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>9400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>8600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>8700</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM48" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="3">
+        <v>117700</v>
+      </c>
+      <c r="F49" s="3">
         <v>118200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>124200</v>
       </c>
-      <c r="F49" s="3">
-        <v>121100</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I49" s="3">
         <v>123100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>126500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>124100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>126100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>134400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>131300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>129900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>131900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>133100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>133400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>138500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>139800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>142500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>139300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>148700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>150000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>161900</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>10</v>
       </c>
@@ -4721,11 +4943,11 @@
       <c r="AB49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE49" s="3">
         <v>0</v>
@@ -4748,8 +4970,14 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +5083,14 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5196,127 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="3">
+        <v>70900</v>
+      </c>
+      <c r="F52" s="3">
         <v>82400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>96200</v>
       </c>
-      <c r="F52" s="3">
-        <v>98700</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" s="3">
         <v>106100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>141900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>179200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>186000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>190100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>332500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>333600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>339300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>320600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>297300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>279600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>241400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>202900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>191200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>183300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>176700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>177400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>108200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>98300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>67800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>54000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>29900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>42900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>38800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>18600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>17700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>12400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>8400</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM52" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5422,127 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3117100</v>
+      </c>
+      <c r="F54" s="3">
         <v>3047100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3211200</v>
       </c>
-      <c r="F54" s="3">
-        <v>3167700</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I54" s="3">
         <v>3225300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3263400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3249200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3294300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3580800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3210200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3149800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3067300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2945600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2903300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2924100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2860800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2819200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2832000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3262900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3229800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3192300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2962000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2586100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2003200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1826400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1811100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1749600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>2113200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>2466200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>2186000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1866600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1734300</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM54" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5580,10 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,543 +5621,575 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F57" s="3">
         <v>10200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F57" s="3">
-        <v>5900</v>
       </c>
       <c r="G57" s="3">
         <v>4600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>8400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>6100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>6000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>9700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>8700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>14800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>31100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>31800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>38800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>21900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>19700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>29800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>27100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>18600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>29400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>9700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>11700</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK57" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM57" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="3">
+        <v>549600</v>
+      </c>
+      <c r="F58" s="3">
         <v>477400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>502600</v>
       </c>
-      <c r="F58" s="3">
-        <v>406500</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I58" s="3">
         <v>434900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>639100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>746500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>799400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1137800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1073800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1002500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>648600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>571500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>676700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>699600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>755800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>912700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>906600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1003500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1045300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1007500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>882800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>701900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>657800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>605900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>738400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>951600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1402200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1893600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1587100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1618800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>1541700</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK58" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM58" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="3">
+        <v>266900</v>
+      </c>
+      <c r="F59" s="3">
         <v>666300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>344600</v>
       </c>
-      <c r="F59" s="3">
-        <v>379700</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I59" s="3">
         <v>427200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>963500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>426300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>354500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>323600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>682200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>666200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>665700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>696400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>727700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>721300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>719300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>680900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>760500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1045100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1055700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1077900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>595500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>535200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>442300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>415200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>406500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>321700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>293700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>242300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>292200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>186800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>158000</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM59" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1364000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1315800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1561500</v>
       </c>
-      <c r="F60" s="3">
-        <v>1452700</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I60" s="3">
         <v>1529600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1738100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1729100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1632600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1926700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1759700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1673400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1322600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1271400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1406600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1423600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1480400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1599700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1673100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2058300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2109800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2100300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1509400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1269000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1138900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1043000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1164600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1303200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1723000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2154400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1908700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>1815300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>1711400</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK60" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM60" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>194400</v>
+      </c>
+      <c r="F61" s="3">
         <v>247300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>152400</v>
       </c>
-      <c r="F61" s="3">
-        <v>316600</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>310300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>145400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>171500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>362500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>334500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>209300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>299600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>578700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>507700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>356200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>371700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>358500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>308400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>382200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>469300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>440800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>441600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>384400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>338000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>32100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>22900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>52200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>47300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>35300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>24800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>19900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>5000</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5925,63 +6217,63 @@
       <c r="K62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N62" s="3">
         <v>21900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>22200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>29500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>29300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>26500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>26000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>8200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>7400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>6800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>10300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>11700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>10000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>52000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>51700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>42600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>33400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>27200</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5994,17 +6286,23 @@
       <c r="AH62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ62" s="3">
-        <v>0</v>
+      <c r="AI62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6408,14 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6521,14 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6634,127 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1572500</v>
+      </c>
+      <c r="F66" s="3">
         <v>1575600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1725100</v>
       </c>
-      <c r="F66" s="3">
-        <v>1779100</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I66" s="3">
         <v>1848900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1894100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1909900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2001800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2268600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1990900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2000800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1936500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1817100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1794800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1827100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1852900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1921300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2067700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2537800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2562200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2551900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1945800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1658700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1185500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1108400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1214700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1355400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1770300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2189700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1933500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1835100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1716400</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM66" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6792,10 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6901,14 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +7014,14 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6777,22 +7113,28 @@
         <v>0</v>
       </c>
       <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
         <v>100100</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AJ70" s="3">
         <v>97600</v>
       </c>
-      <c r="AI70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ70" s="3">
-        <v>0</v>
-      </c>
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7240,127 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1131900</v>
+      </c>
+      <c r="F72" s="3">
         <v>1066300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1070100</v>
       </c>
-      <c r="F72" s="3">
-        <v>989400</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I72" s="3">
         <v>976200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>965600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>955300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>910100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>909000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>834200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>775800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>742400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>719500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>703800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>688200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>605600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>499000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>384600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>332100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>281300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>235000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>629300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>549500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>443800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>361300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>260300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>74600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>30400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-35600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-58600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-72800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-82900</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM72" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7466,14 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7579,14 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7692,127 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1544600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1471400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1486100</v>
       </c>
-      <c r="F76" s="3">
-        <v>1388600</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I76" s="3">
         <v>1376400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1369400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1339200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1292500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1312200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1219300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1149000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1130800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1128400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1108500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1097000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1007800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>898000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>764300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>725000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>667500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>640500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1016200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>927400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>817700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>718000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>596400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>394200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>342900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>276500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>252500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>-68600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>-79700</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM76" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7918,245 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F81" s="3">
         <v>49700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>44100</v>
       </c>
-      <c r="F81" s="3">
-        <v>31200</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I81" s="3">
         <v>27900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>50800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>49100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>47700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>42500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>38100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>22900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>10900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>35300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>82500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>111800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>102200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>70900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>50800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>61700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-107000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>79700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>111500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>98000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>64500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>152400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>62600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>92900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>25500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>3200</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>800</v>
-      </c>
-      <c r="AH81" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI81" s="3">
         <v>800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AJ81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AL81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +8194,10 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7827,11 +8225,11 @@
       <c r="K83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7888,14 +8286,14 @@
         <v>0</v>
       </c>
       <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
         <v>800</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI83" s="3" t="s">
         <v>10</v>
       </c>
@@ -7905,8 +8303,14 @@
       <c r="AK83" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM83" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8416,14 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8529,14 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8642,14 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8755,14 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,8 +8868,14 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8469,11 +8903,11 @@
       <c r="K89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -8530,14 +8964,14 @@
         <v>0</v>
       </c>
       <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
         <v>99300</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>10</v>
       </c>
@@ -8547,8 +8981,14 @@
       <c r="AK89" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM89" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,8 +9026,10 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8615,11 +9057,11 @@
       <c r="K91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8676,14 +9118,14 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-800</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>10</v>
       </c>
@@ -8693,8 +9135,14 @@
       <c r="AK91" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM91" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9248,14 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,8 +9361,14 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8936,11 +9396,11 @@
       <c r="K94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -8997,14 +9457,14 @@
         <v>0</v>
       </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-187300</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>10</v>
       </c>
@@ -9014,8 +9474,14 @@
       <c r="AK94" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM94" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9519,10 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,11 +9550,11 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9160,8 +9628,14 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9741,14 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9854,14 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,8 +9967,14 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9510,11 +10002,11 @@
       <c r="K100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9571,14 +10063,14 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>180500</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI100" s="3" t="s">
         <v>10</v>
       </c>
@@ -9588,8 +10080,14 @@
       <c r="AK100" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM100" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,11 +10115,11 @@
       <c r="K101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9678,14 +10176,14 @@
         <v>0</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-200</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI101" s="3" t="s">
         <v>10</v>
       </c>
@@ -9695,8 +10193,14 @@
       <c r="AK101" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM101" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9724,11 +10228,11 @@
       <c r="K102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -9785,14 +10289,14 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>92300</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI102" s="3" t="s">
         <v>10</v>
       </c>
@@ -9800,6 +10304,12 @@
         <v>10</v>
       </c>
       <c r="AK102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM102" s="3" t="s">
         <v>10</v>
       </c>
     </row>
